--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="1677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1678">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5043,6 +5043,9 @@
   </si>
   <si>
     <t xml:space="preserve">25.2999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -70043,7 +70046,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495717593</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>1529479</v>
@@ -70064,6 +70067,32 @@
         <v>1676</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494212963</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>1798395</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>25.2199993133545</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>23.9599990844727</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="1679">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5046,6 +5046,9 @@
   </si>
   <si>
     <t xml:space="preserve">24.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -70072,7 +70075,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494212963</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1798395</v>
@@ -70093,6 +70096,32 @@
         <v>1677</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6522453704</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>2544665</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>25.0200004577637</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="1679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="1680">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5049,6 +5049,9 @@
   </si>
   <si>
     <t xml:space="preserve">23.2399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0599994659424</t>
   </si>
 </sst>
 </file>
@@ -70127,7 +70130,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6494675926</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>2037701</v>
@@ -70148,6 +70151,32 @@
         <v>1678</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6525925926</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>1985199</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>22.7600002288818</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>21.8400001525879</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>22.4200000762939</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>22.0599994659424</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="1684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1685">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5064,6 +5064,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0599994659424</t>
   </si>
 </sst>
 </file>
@@ -70246,7 +70249,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6497106481</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1184061</v>
@@ -70267,6 +70270,32 @@
         <v>1683</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6496759259</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>729068</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>23.5599994659424</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>23.1399993896484</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>23.0599994659424</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="1686">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5067,6 +5067,9 @@
   </si>
   <si>
     <t xml:space="preserve">23.0599994659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0200004577637</t>
   </si>
 </sst>
 </file>
@@ -70275,7 +70278,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6496759259</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>729068</v>
@@ -70296,6 +70299,32 @@
         <v>1684</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6497685185</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>810549</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>22.7399997711182</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>23.0200004577637</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1685</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="1688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="1689">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5076,6 +5076,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.2999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5200004577637</t>
   </si>
 </sst>
 </file>
@@ -70388,7 +70391,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6910069444</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>1182284</v>
@@ -70409,6 +70412,32 @@
         <v>1687</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6914814815</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>800917</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>22.4599990844727</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>21.9200000762939</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>22.3199996948242</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>22.5200004577637</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="1693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="1694">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5091,6 +5091,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.7199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1599998474121</t>
   </si>
 </sst>
 </file>
@@ -70507,7 +70510,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6918865741</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>854152</v>
@@ -70528,6 +70531,32 @@
         <v>1692</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6910648148</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>1100298</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>21.7600002288818</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>20.9200000762939</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>21.6599998474121</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>21.1599998474121</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1693</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">21.7199993133545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1599998474121</t>
+    <t xml:space="preserve">20.6399993896484</t>
   </si>
 </sst>
 </file>
@@ -70536,22 +70536,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6910648148</v>
+        <v>45967.6944097222</v>
       </c>
       <c r="B2505" t="n">
-        <v>1100298</v>
+        <v>1241649</v>
       </c>
       <c r="C2505" t="n">
-        <v>21.7600002288818</v>
+        <v>21.3199996948242</v>
       </c>
       <c r="D2505" t="n">
-        <v>20.9200000762939</v>
+        <v>20.2199993133545</v>
       </c>
       <c r="E2505" t="n">
-        <v>21.6599998474121</v>
+        <v>21.2800006866455</v>
       </c>
       <c r="F2505" t="n">
-        <v>21.1599998474121</v>
+        <v>20.6399993896484</v>
       </c>
       <c r="G2505" t="s">
         <v>1693</v>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="1697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1698">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5103,6 +5103,9 @@
   </si>
   <si>
     <t xml:space="preserve">20.2399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -70649,7 +70652,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6919675926</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>1845157</v>
@@ -70670,6 +70673,32 @@
         <v>1696</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6924884259</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>4447961</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>18.9200000762939</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1697</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70736,7 +70736,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6912615741</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>2104843</v>
@@ -70757,6 +70757,32 @@
         <v>1699</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6911921296</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>1253670</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>19.0900001525879</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>18.6499996185303</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>18.8500003814697</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>18.9899997711182</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1700" uniqueCount="1700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1701">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5112,6 +5112,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.8899993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7399997711182</t>
   </si>
 </sst>
 </file>
@@ -70762,7 +70765,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911921296</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>1253670</v>
@@ -70783,6 +70786,32 @@
         <v>1649</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6922337963</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>1208055</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>19.1399993896484</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>18.7399997711182</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1702">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5115,6 +5115,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.7399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6000003814697</t>
   </si>
 </sst>
 </file>
@@ -70791,7 +70794,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6922337963</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>1208055</v>
@@ -70812,6 +70815,32 @@
         <v>1700</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6919444444</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>1261599</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>19.0799999237061</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>18.4099998474121</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1701</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="1704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="1705">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5124,6 +5124,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.6800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9300003051758</t>
   </si>
 </sst>
 </file>
@@ -70852,7 +70855,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6912731481</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>1078801</v>
@@ -70873,6 +70876,32 @@
         <v>1703</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6913657407</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>1690803</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>18.2800006866455</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>17.6399993896484</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>18.1200008392334</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>17.9300003051758</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="1705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="1706">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5127,6 +5127,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.9300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8199996948242</t>
   </si>
 </sst>
 </file>
@@ -70881,7 +70884,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6913657407</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>1690803</v>
@@ -70902,6 +70905,32 @@
         <v>1704</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.691099537</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>1180476</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>18.0799999237061</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>17.9599990844727</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="1706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="1707">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5130,6 +5130,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6200008392334</t>
   </si>
 </sst>
 </file>
@@ -70910,7 +70913,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.691099537</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>1180476</v>
@@ -70931,6 +70934,32 @@
         <v>1705</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.692662037</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>1553700</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>17.7800006866455</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>17.2000007629395</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>17.5799999237061</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>17.6200008392334</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1706</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="1707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="1708">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5133,6 +5133,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.6200008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599990844727</t>
   </si>
 </sst>
 </file>
@@ -70939,7 +70942,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.692662037</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>1553700</v>
@@ -70960,6 +70963,32 @@
         <v>1706</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6938194444</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>1875451</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>17.8199996948242</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>16.7399997711182</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>17.4200000762939</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="1708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1709">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5136,6 +5136,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2600002288818</t>
   </si>
 </sst>
 </file>
@@ -70968,7 +70971,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6938194444</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>1875451</v>
@@ -70989,6 +70992,32 @@
         <v>1707</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6917592593</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>841688</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>17.5599994659424</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>17.2600002288818</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70997,7 +70997,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6917592593</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>841688</v>
@@ -71018,6 +71018,32 @@
         <v>1708</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.691400463</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>982280</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>16.9400005340576</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>17.2999992370605</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>17.0100002288818</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="1710">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5139,6 +5139,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6499996185303</t>
   </si>
 </sst>
 </file>
@@ -71023,7 +71026,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.691400463</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>982280</v>
@@ -71044,6 +71047,32 @@
         <v>1630</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6935300926</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>1370560</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>17.0300006866455</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>16.3799991607666</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>16.9200000762939</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>16.6499996185303</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="1710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="1711">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5142,6 +5142,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.6499996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8299999237061</t>
   </si>
 </sst>
 </file>
@@ -71052,7 +71055,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6935300926</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>1370560</v>
@@ -71073,6 +71076,32 @@
         <v>1709</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6913078704</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>946135</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>16.9400005340576</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>16.3700008392334</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>16.8299999237061</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1710</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="1711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="1712">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5145,6 +5145,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.6200008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2099990844727</t>
   </si>
 </sst>
 </file>
@@ -71107,7 +71110,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6909953704</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>1015350</v>
@@ -71128,6 +71131,32 @@
         <v>1710</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6911342593</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>1645673</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>17.3400001525879</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>16.8500003814697</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>17.0300006866455</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>17.2099990844727</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1711</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="1712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1713">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5148,6 +5148,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2099990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6299991607666</t>
   </si>
 </sst>
 </file>
@@ -71136,7 +71139,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6911342593</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>1645673</v>
@@ -71157,6 +71160,32 @@
         <v>1711</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6911458333</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>2178736</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>18.1800003051758</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>17.3199996948242</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>17.3899993896484</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>17.6299991607666</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="1713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="1714">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5151,6 +5151,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.6299991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3899993896484</t>
   </si>
 </sst>
 </file>
@@ -71165,7 +71168,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6911458333</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>2178736</v>
@@ -71186,6 +71189,32 @@
         <v>1712</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6910763889</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>1708340</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>18.5200004577637</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>17.8899993896484</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>18.0499992370605</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>18.3899993896484</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1713</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="1714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="1715">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5154,6 +5154,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.3899993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0699996948242</t>
   </si>
 </sst>
 </file>
@@ -71194,7 +71197,7 @@
     </row>
     <row r="2528">
       <c r="A2528" s="1" t="n">
-        <v>45999.6910763889</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2528" t="n">
         <v>1708340</v>
@@ -71215,6 +71218,32 @@
         <v>1713</v>
       </c>
       <c r="H2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="1" t="n">
+        <v>46000.6910185185</v>
+      </c>
+      <c r="B2529" t="n">
+        <v>2497705</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>18.4300003051758</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>18.5599994659424</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>19.0699996948242</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>1714</v>
+      </c>
+      <c r="H2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1715" uniqueCount="1715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="1716">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5157,6 +5157,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.0699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3799991607666</t>
   </si>
 </sst>
 </file>
@@ -71223,7 +71226,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6910185185</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>2497705</v>
@@ -71244,6 +71247,32 @@
         <v>1714</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6912152778</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>1642070</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>19.0499992370605</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>19.0200004577637</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>18.3799991607666</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="1717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="1718">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5163,6 +5163,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.4400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4599990844727</t>
   </si>
 </sst>
 </file>
@@ -71307,7 +71310,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6911574074</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>907850</v>
@@ -71328,6 +71331,32 @@
         <v>1638</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6919791667</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>988294</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>18.4599990844727</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>18.0699996948242</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>18.4599990844727</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="1723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="1724">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5181,6 +5181,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.5100002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8400001525879</t>
   </si>
 </sst>
 </file>
@@ -71481,7 +71484,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.6911574074</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>1490049</v>
@@ -71502,6 +71505,32 @@
         <v>1722</v>
       </c>
       <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.6911921296</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>1829844</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>16.9200000762939</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>16.5300006866455</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>16.6299991607666</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>16.8400001525879</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>1723</v>
+      </c>
+      <c r="H2539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71510,7 +71510,7 @@
     </row>
     <row r="2539">
       <c r="A2539" s="1" t="n">
-        <v>46014.6911921296</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2539" t="n">
         <v>1829844</v>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71534,6 +71534,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6924768519</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>1718686</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>16.7000007629395</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>16.2199993133545</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>16.6700000762939</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>16.5499992370605</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="1724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1725">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5184,6 +5184,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.8400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7000007629395</t>
   </si>
 </sst>
 </file>
@@ -71536,7 +71539,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.6924768519</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>1718686</v>
@@ -71557,6 +71560,32 @@
         <v>1624</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6937962963</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>1286029</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>16.7199993133545</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>16.4799995422363</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>16.5699996948242</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>16.7000007629395</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>1724</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="1726">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5187,6 +5187,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.6599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -71591,7 +71594,7 @@
     </row>
     <row r="2542">
       <c r="A2542" s="1" t="n">
-        <v>46024.6913194444</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2542" t="n">
         <v>3063382</v>
@@ -71612,6 +71615,32 @@
         <v>1724</v>
       </c>
       <c r="H2542" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="1" t="n">
+        <v>46027.6930787037</v>
+      </c>
+      <c r="B2543" t="n">
+        <v>3517659</v>
+      </c>
+      <c r="C2543" t="n">
+        <v>18.6800003051758</v>
+      </c>
+      <c r="D2543" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="E2543" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="F2543" t="n">
+        <v>18.4500007629395</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>1725</v>
+      </c>
+      <c r="H2543" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="1728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="1729">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5196,6 +5196,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.3299999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3700008392334</t>
   </si>
 </sst>
 </file>
@@ -71678,7 +71681,7 @@
     </row>
     <row r="2545">
       <c r="A2545" s="1" t="n">
-        <v>46029.6932407407</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2545" t="n">
         <v>3555743</v>
@@ -71699,6 +71702,32 @@
         <v>1727</v>
       </c>
       <c r="H2545" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="1" t="n">
+        <v>46030.6912615741</v>
+      </c>
+      <c r="B2546" t="n">
+        <v>4438592</v>
+      </c>
+      <c r="C2546" t="n">
+        <v>20.1000003814697</v>
+      </c>
+      <c r="D2546" t="n">
+        <v>19.0200004577637</v>
+      </c>
+      <c r="E2546" t="n">
+        <v>19.5799999237061</v>
+      </c>
+      <c r="F2546" t="n">
+        <v>19.3700008392334</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>1728</v>
+      </c>
+      <c r="H2546" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="1729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="1730">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5199,6 +5199,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.3700008392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4899997711182</t>
   </si>
 </sst>
 </file>
@@ -71707,7 +71710,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6912615741</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>4438592</v>
@@ -71728,6 +71731,32 @@
         <v>1728</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6915162037</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>1960156</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>19.5900001525879</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>19.4899997711182</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>19.4899997711182</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="1731">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5202,6 +5202,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.4899997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3600006103516</t>
   </si>
 </sst>
 </file>
@@ -71788,7 +71791,7 @@
     </row>
     <row r="2549">
       <c r="A2549" s="1" t="n">
-        <v>46035.6913078704</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2549" t="n">
         <v>4936940</v>
@@ -71809,6 +71812,32 @@
         <v>1727</v>
       </c>
       <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46036.6910763889</v>
+      </c>
+      <c r="B2550" t="n">
+        <v>2952288</v>
+      </c>
+      <c r="C2550" t="n">
+        <v>19.6100006103516</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>18.8299999237061</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>19.4200000762939</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>19.3600006103516</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H2550" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="1736">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5217,6 +5217,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.6299991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1700000762939</t>
   </si>
 </sst>
 </file>
@@ -71907,7 +71910,7 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.6916319444</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>3458507</v>
@@ -71928,6 +71931,32 @@
         <v>1734</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6912615741</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>2267560</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>19.6299991607666</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>19.6000003814697</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>19.1700000762939</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71936,7 +71936,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6912615741</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>2267560</v>
@@ -71957,6 +71957,32 @@
         <v>1735</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.691087963</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>2355845</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>19.2999992370605</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>19.2800006866455</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>18.4400005340576</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="1736">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5217,6 +5217,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.1700000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0499992370605</t>
   </si>
 </sst>
 </file>
@@ -71985,7 +71988,7 @@
     </row>
     <row r="2556">
       <c r="A2556" s="1" t="n">
-        <v>46044.6941666667</v>
+        <v>46044.3333333333</v>
       </c>
       <c r="B2556" t="n">
         <v>7952732</v>
@@ -72006,6 +72009,32 @@
         <v>1709</v>
       </c>
       <c r="H2556" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="1" t="n">
+        <v>46045.6911574074</v>
+      </c>
+      <c r="B2557" t="n">
+        <v>4016202</v>
+      </c>
+      <c r="C2557" t="n">
+        <v>17.3099994659424</v>
+      </c>
+      <c r="D2557" t="n">
+        <v>16.7199993133545</v>
+      </c>
+      <c r="E2557" t="n">
+        <v>16.7999992370605</v>
+      </c>
+      <c r="F2557" t="n">
+        <v>17.0499992370605</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H2557" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1738">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5223,6 +5223,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6700000762939</t>
   </si>
 </sst>
 </file>
@@ -72043,7 +72046,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.6923148148</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>3488893</v>
@@ -72064,6 +72067,32 @@
         <v>1709</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.6910532407</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>2249650</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>16.9599990844727</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>16.4799995422363</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>16.7800006866455</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>16.6700000762939</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="1739">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5226,6 +5226,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.6700000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.75</t>
   </si>
 </sst>
 </file>
@@ -72072,7 +72075,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.6910532407</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>2249650</v>
@@ -72093,6 +72096,32 @@
         <v>1737</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6941203704</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>2183651</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>17.0200004577637</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>16.6000003814697</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>16.8400001525879</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>1738</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -72101,7 +72101,7 @@
     </row>
     <row r="2560">
       <c r="A2560" s="1" t="n">
-        <v>46050.6941203704</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B2560" t="n">
         <v>2183651</v>
@@ -72122,6 +72122,32 @@
         <v>1738</v>
       </c>
       <c r="H2560" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" s="1" t="n">
+        <v>46051.6914236111</v>
+      </c>
+      <c r="B2561" t="n">
+        <v>1680539</v>
+      </c>
+      <c r="C2561" t="n">
+        <v>16.9500007629395</v>
+      </c>
+      <c r="D2561" t="n">
+        <v>16.3799991607666</v>
+      </c>
+      <c r="E2561" t="n">
+        <v>16.7600002288818</v>
+      </c>
+      <c r="F2561" t="n">
+        <v>16.6700000762939</v>
+      </c>
+      <c r="G2561" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H2561" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="1741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="1742">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5235,6 +5235,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.8900003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9799995422363</t>
   </si>
 </sst>
 </file>
@@ -72185,7 +72188,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.691087963</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>2411280</v>
@@ -72206,6 +72209,32 @@
         <v>1740</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6909722222</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>2184428</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>16.1299991607666</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>15.6599998474121</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>16.0599994659424</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>15.9799995422363</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="1741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="1742">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5235,6 +5235,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.9799995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.539999961853</t>
   </si>
 </sst>
 </file>
@@ -72237,7 +72240,7 @@
     </row>
     <row r="2565">
       <c r="A2565" s="1" t="n">
-        <v>46057.6910300926</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2565" t="n">
         <v>2859543</v>
@@ -72258,6 +72261,32 @@
         <v>1593</v>
       </c>
       <c r="H2565" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="1" t="n">
+        <v>46058.6926157407</v>
+      </c>
+      <c r="B2566" t="n">
+        <v>3221814</v>
+      </c>
+      <c r="C2566" t="n">
+        <v>15.9300003051758</v>
+      </c>
+      <c r="D2566" t="n">
+        <v>15.1300001144409</v>
+      </c>
+      <c r="E2566" t="n">
+        <v>15.5900001525879</v>
+      </c>
+      <c r="F2566" t="n">
+        <v>15.539999961853</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H2566" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -72298,7 +72298,7 @@
     </row>
     <row r="2567">
       <c r="A2567" s="1" t="n">
-        <v>46059.6918055556</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2567" t="n">
         <v>2098519</v>
@@ -72319,6 +72319,32 @@
         <v>1743</v>
       </c>
       <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.6909953704</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>2453566</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>15.6899995803833</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>15.7200002670288</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>16.0900001525879</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H2568" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="1744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1745">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5244,6 +5244,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.6099996566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1299991607666</t>
   </si>
 </sst>
 </file>
@@ -72324,7 +72327,7 @@
     </row>
     <row r="2568">
       <c r="A2568" s="1" t="n">
-        <v>46062.6909953704</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2568" t="n">
         <v>2453566</v>
@@ -72345,6 +72348,32 @@
         <v>1631</v>
       </c>
       <c r="H2568" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" s="1" t="n">
+        <v>46063.6912037037</v>
+      </c>
+      <c r="B2569" t="n">
+        <v>2231174</v>
+      </c>
+      <c r="C2569" t="n">
+        <v>16.3600006103516</v>
+      </c>
+      <c r="D2569" t="n">
+        <v>16.0200004577637</v>
+      </c>
+      <c r="E2569" t="n">
+        <v>16.2900009155273</v>
+      </c>
+      <c r="F2569" t="n">
+        <v>16.1299991607666</v>
+      </c>
+      <c r="G2569" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H2569" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="1745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1746">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5247,6 +5247,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.1299991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0400009155273</t>
   </si>
 </sst>
 </file>
@@ -72353,7 +72356,7 @@
     </row>
     <row r="2569">
       <c r="A2569" s="1" t="n">
-        <v>46063.6912037037</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2569" t="n">
         <v>2231174</v>
@@ -72374,6 +72377,32 @@
         <v>1744</v>
       </c>
       <c r="H2569" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" s="1" t="n">
+        <v>46064.6911342593</v>
+      </c>
+      <c r="B2570" t="n">
+        <v>2307737</v>
+      </c>
+      <c r="C2570" t="n">
+        <v>16.4799995422363</v>
+      </c>
+      <c r="D2570" t="n">
+        <v>15.9099998474121</v>
+      </c>
+      <c r="E2570" t="n">
+        <v>16.0200004577637</v>
+      </c>
+      <c r="F2570" t="n">
+        <v>16.0400009155273</v>
+      </c>
+      <c r="G2570" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H2570" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="1746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1747">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5250,6 +5250,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.0400009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5</t>
   </si>
 </sst>
 </file>
@@ -72382,7 +72385,7 @@
     </row>
     <row r="2570">
       <c r="A2570" s="1" t="n">
-        <v>46064.6911342593</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B2570" t="n">
         <v>2307737</v>
@@ -72403,6 +72406,32 @@
         <v>1745</v>
       </c>
       <c r="H2570" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" s="1" t="n">
+        <v>46065.6911226852</v>
+      </c>
+      <c r="B2571" t="n">
+        <v>3912615</v>
+      </c>
+      <c r="C2571" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2571" t="n">
+        <v>16.3199996948242</v>
+      </c>
+      <c r="E2571" t="n">
+        <v>16.3600006103516</v>
+      </c>
+      <c r="F2571" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G2571" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H2571" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="1748">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5253,6 +5253,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -72411,7 +72414,7 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46065.6911226852</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2571" t="n">
         <v>3912615</v>
@@ -72432,6 +72435,32 @@
         <v>1746</v>
       </c>
       <c r="H2571" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="1" t="n">
+        <v>46066.6936226852</v>
+      </c>
+      <c r="B2572" t="n">
+        <v>1860725</v>
+      </c>
+      <c r="C2572" t="n">
+        <v>16.6200008392334</v>
+      </c>
+      <c r="D2572" t="n">
+        <v>16.0100002288818</v>
+      </c>
+      <c r="E2572" t="n">
+        <v>16.6200008392334</v>
+      </c>
+      <c r="F2572" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>1747</v>
+      </c>
+      <c r="H2572" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="1747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="1748">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5253,6 +5253,9 @@
   </si>
   <si>
     <t xml:space="preserve">16.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1700000762939</t>
   </si>
 </sst>
 </file>
@@ -72463,7 +72466,7 @@
     </row>
     <row r="2573">
       <c r="A2573" s="1" t="n">
-        <v>46069.6940856482</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B2573" t="n">
         <v>2063348</v>
@@ -72484,6 +72487,32 @@
         <v>1737</v>
       </c>
       <c r="H2573" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" s="1" t="n">
+        <v>46070.6910416667</v>
+      </c>
+      <c r="B2574" t="n">
+        <v>3126162</v>
+      </c>
+      <c r="C2574" t="n">
+        <v>16.6499996185303</v>
+      </c>
+      <c r="D2574" t="n">
+        <v>15.9200000762939</v>
+      </c>
+      <c r="E2574" t="n">
+        <v>16.5900001525879</v>
+      </c>
+      <c r="F2574" t="n">
+        <v>16.1700000762939</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>1747</v>
+      </c>
+      <c r="H2574" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -72492,7 +72492,7 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46070.6910416667</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B2574" t="n">
         <v>3126162</v>
@@ -72513,6 +72513,32 @@
         <v>1747</v>
       </c>
       <c r="H2574" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46071.6917592593</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>2795445</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>16.7199993133545</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>16.1599998474121</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>16.4699993133545</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H2575" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1751">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5262,6 +5262,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.960000038147</t>
   </si>
 </sst>
 </file>
@@ -72550,7 +72553,7 @@
     </row>
     <row r="2576">
       <c r="A2576" s="1" t="n">
-        <v>46072.6942013889</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2576" t="n">
         <v>50541221</v>
@@ -72571,6 +72574,32 @@
         <v>1749</v>
       </c>
       <c r="H2576" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="1" t="n">
+        <v>46073.6912962963</v>
+      </c>
+      <c r="B2577" t="n">
+        <v>6256205</v>
+      </c>
+      <c r="C2577" t="n">
+        <v>15.1199998855591</v>
+      </c>
+      <c r="D2577" t="n">
+        <v>14.5200004577637</v>
+      </c>
+      <c r="E2577" t="n">
+        <v>14.5600004196167</v>
+      </c>
+      <c r="F2577" t="n">
+        <v>14.960000038147</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H2577" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -72631,7 +72631,7 @@
     </row>
     <row r="2579">
       <c r="A2579" s="1" t="n">
-        <v>46077.69125</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B2579" t="n">
         <v>2967814</v>
@@ -72652,6 +72652,32 @@
         <v>1601</v>
       </c>
       <c r="H2579" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" s="1" t="n">
+        <v>46078.6931597222</v>
+      </c>
+      <c r="B2580" t="n">
+        <v>4483453</v>
+      </c>
+      <c r="C2580" t="n">
+        <v>14.9300003051758</v>
+      </c>
+      <c r="D2580" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="E2580" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2580" t="n">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="G2580" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H2580" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="1752">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5265,6 +5265,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.6400003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4300003051758</t>
   </si>
 </sst>
 </file>
@@ -72683,7 +72686,7 @@
     </row>
     <row r="2581">
       <c r="A2581" s="1" t="n">
-        <v>46079.6915277778</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2581" t="n">
         <v>3551623</v>
@@ -72704,6 +72707,32 @@
         <v>1750</v>
       </c>
       <c r="H2581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46080.6943981481</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>3743642</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>14.6700000762939</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>14.6499996185303</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>14.4300003051758</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>1751</v>
+      </c>
+      <c r="H2582" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -72712,7 +72712,7 @@
     </row>
     <row r="2582">
       <c r="A2582" s="1" t="n">
-        <v>46080.6943981481</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B2582" t="n">
         <v>3743642</v>
@@ -72733,6 +72733,32 @@
         <v>1751</v>
       </c>
       <c r="H2582" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" s="1" t="n">
+        <v>46083.6911574074</v>
+      </c>
+      <c r="B2583" t="n">
+        <v>6041894</v>
+      </c>
+      <c r="C2583" t="n">
+        <v>15.0600004196167</v>
+      </c>
+      <c r="D2583" t="n">
+        <v>14.3699998855591</v>
+      </c>
+      <c r="E2583" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="F2583" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H2583" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="1754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1755">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5274,6 +5274,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.8000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3900003433228</t>
   </si>
 </sst>
 </file>
@@ -72770,7 +72773,7 @@
     </row>
     <row r="2584">
       <c r="A2584" s="1" t="n">
-        <v>46084.6927199074</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2584" t="n">
         <v>5870418</v>
@@ -72791,6 +72794,32 @@
         <v>1753</v>
       </c>
       <c r="H2584" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46085.6935648148</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>3289187</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>13.6199998855591</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>13.6199998855591</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>14.3900003433228</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H2585" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="1756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="1757">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5280,6 +5280,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.8699998855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0600004196167</t>
   </si>
 </sst>
 </file>
@@ -72880,7 +72883,7 @@
     </row>
     <row r="2588">
       <c r="A2588" s="1" t="n">
-        <v>46090.6926041667</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B2588" t="n">
         <v>2531758</v>
@@ -72901,6 +72904,32 @@
         <v>1755</v>
       </c>
       <c r="H2588" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" s="1" t="n">
+        <v>46091.6941319444</v>
+      </c>
+      <c r="B2589" t="n">
+        <v>2324715</v>
+      </c>
+      <c r="C2589" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="D2589" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2589" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F2589" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="G2589" t="s">
+        <v>1756</v>
+      </c>
+      <c r="H2589" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="1757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="1758">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5283,6 +5283,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.0600004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6999998092651</t>
   </si>
 </sst>
 </file>
@@ -72909,7 +72912,7 @@
     </row>
     <row r="2589">
       <c r="A2589" s="1" t="n">
-        <v>46091.6941319444</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B2589" t="n">
         <v>2324715</v>
@@ -72930,6 +72933,32 @@
         <v>1756</v>
       </c>
       <c r="H2589" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" s="1" t="n">
+        <v>46092.69125</v>
+      </c>
+      <c r="B2590" t="n">
+        <v>2361713</v>
+      </c>
+      <c r="C2590" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D2590" t="n">
+        <v>13.5900001525879</v>
+      </c>
+      <c r="E2590" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="F2590" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>1757</v>
+      </c>
+      <c r="H2590" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1762">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5292,6 +5292,12 @@
   </si>
   <si>
     <t xml:space="preserve">13.7299995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2700004577637</t>
   </si>
 </sst>
 </file>
@@ -72970,7 +72976,7 @@
     </row>
     <row r="2591">
       <c r="A2591" s="1" t="n">
-        <v>46093.6921759259</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B2591" t="n">
         <v>3262042</v>
@@ -72991,6 +72997,56 @@
         <v>1759</v>
       </c>
       <c r="H2591" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2592" t="n">
+        <v>2939311</v>
+      </c>
+      <c r="C2592" t="n">
+        <v>13.8100004196167</v>
+      </c>
+      <c r="D2592" t="n">
+        <v>13.210000038147</v>
+      </c>
+      <c r="E2592" t="n">
+        <v>13.6099996566772</v>
+      </c>
+      <c r="F2592"/>
+      <c r="G2592" t="s">
+        <v>1760</v>
+      </c>
+      <c r="H2592" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="1" t="n">
+        <v>46094.6944212963</v>
+      </c>
+      <c r="B2593" t="n">
+        <v>2939311</v>
+      </c>
+      <c r="C2593" t="n">
+        <v>13.8100004196167</v>
+      </c>
+      <c r="D2593" t="n">
+        <v>13.210000038147</v>
+      </c>
+      <c r="E2593" t="n">
+        <v>13.6099996566772</v>
+      </c>
+      <c r="F2593" t="n">
+        <v>13.2700004577637</v>
+      </c>
+      <c r="G2593" t="s">
+        <v>1761</v>
+      </c>
+      <c r="H2593" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1763" uniqueCount="1763">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5294,10 +5294,13 @@
     <t xml:space="preserve">13.2700004577637</t>
   </si>
   <si>
+    <t xml:space="preserve">13.3100004196167</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">13.3100004196167</t>
+    <t xml:space="preserve">13.039999961853</t>
   </si>
 </sst>
 </file>
@@ -73042,7 +73045,9 @@
       <c r="E2593" t="n">
         <v>13.3000001907349</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>13.3100004196167</v>
+      </c>
       <c r="G2593" t="s">
         <v>1760</v>
       </c>
@@ -73052,27 +73057,51 @@
     </row>
     <row r="2594">
       <c r="A2594" s="1" t="n">
-        <v>46097.6944328704</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B2594" t="n">
-        <v>1674235</v>
+        <v>2626010</v>
       </c>
       <c r="C2594" t="n">
-        <v>13.5100002288818</v>
+        <v>13.3999996185303</v>
       </c>
       <c r="D2594" t="n">
-        <v>13.1800003051758</v>
+        <v>12.8599996566772</v>
       </c>
       <c r="E2594" t="n">
-        <v>13.3000001907349</v>
-      </c>
-      <c r="F2594" t="n">
-        <v>13.3100004196167</v>
-      </c>
+        <v>13.3999996185303</v>
+      </c>
+      <c r="F2594"/>
       <c r="G2594" t="s">
         <v>1761</v>
       </c>
       <c r="H2594" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46098.6926736111</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>2626010</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>13.3999996185303</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>12.8599996566772</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>13.3999996185303</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>13.039999961853</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>1762</v>
+      </c>
+      <c r="H2595" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="1765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="1766">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5303,10 +5303,13 @@
     <t xml:space="preserve">13.1499996185303</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6400003433228</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">12.6400003433228</t>
+    <t xml:space="preserve">12.5900001525879</t>
   </si>
 </sst>
 </file>
@@ -73129,7 +73132,9 @@
       <c r="E2596" t="n">
         <v>12.9099998474121</v>
       </c>
-      <c r="F2596"/>
+      <c r="F2596" t="n">
+        <v>12.6400003433228</v>
+      </c>
       <c r="G2596" t="s">
         <v>1763</v>
       </c>
@@ -73139,27 +73144,51 @@
     </row>
     <row r="2597">
       <c r="A2597" s="1" t="n">
-        <v>46100.6912152778</v>
+        <v>46101.3333333333</v>
       </c>
       <c r="B2597" t="n">
-        <v>2296754</v>
+        <v>2593722</v>
       </c>
       <c r="C2597" t="n">
-        <v>13.039999961853</v>
+        <v>12.8100004196167</v>
       </c>
       <c r="D2597" t="n">
-        <v>12.5699996948242</v>
+        <v>12.4200000762939</v>
       </c>
       <c r="E2597" t="n">
-        <v>12.9099998474121</v>
-      </c>
-      <c r="F2597" t="n">
-        <v>12.6400003433228</v>
-      </c>
+        <v>12.710000038147</v>
+      </c>
+      <c r="F2597"/>
       <c r="G2597" t="s">
         <v>1764</v>
       </c>
       <c r="H2597" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" s="1" t="n">
+        <v>46101.6938425926</v>
+      </c>
+      <c r="B2598" t="n">
+        <v>2593722</v>
+      </c>
+      <c r="C2598" t="n">
+        <v>12.8100004196167</v>
+      </c>
+      <c r="D2598" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="E2598" t="n">
+        <v>12.710000038147</v>
+      </c>
+      <c r="F2598" t="n">
+        <v>12.5900001525879</v>
+      </c>
+      <c r="G2598" t="s">
+        <v>1765</v>
+      </c>
+      <c r="H2598" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="1768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="1769">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5312,10 +5312,13 @@
     <t xml:space="preserve">12.5900001525879</t>
   </si>
   <si>
+    <t xml:space="preserve">12.8400001525879</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">12.8400001525879</t>
+    <t xml:space="preserve">12.3699998855591</t>
   </si>
 </sst>
 </file>
@@ -73190,7 +73193,9 @@
       <c r="E2598" t="n">
         <v>12.1999998092651</v>
       </c>
-      <c r="F2598"/>
+      <c r="F2598" t="n">
+        <v>12.8400001525879</v>
+      </c>
       <c r="G2598" t="s">
         <v>1766</v>
       </c>
@@ -73200,27 +73205,51 @@
     </row>
     <row r="2599">
       <c r="A2599" s="1" t="n">
-        <v>46104.6912152778</v>
+        <v>46105.3333333333</v>
       </c>
       <c r="B2599" t="n">
-        <v>2794025</v>
+        <v>2712683</v>
       </c>
       <c r="C2599" t="n">
-        <v>12.9799995422363</v>
+        <v>12.7299995422363</v>
       </c>
       <c r="D2599" t="n">
-        <v>12.1499996185303</v>
+        <v>12.2299995422363</v>
       </c>
       <c r="E2599" t="n">
-        <v>12.1999998092651</v>
-      </c>
-      <c r="F2599" t="n">
-        <v>12.8400001525879</v>
-      </c>
+        <v>12.710000038147</v>
+      </c>
+      <c r="F2599"/>
       <c r="G2599" t="s">
         <v>1767</v>
       </c>
       <c r="H2599" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" s="1" t="n">
+        <v>46105.6919675926</v>
+      </c>
+      <c r="B2600" t="n">
+        <v>2712683</v>
+      </c>
+      <c r="C2600" t="n">
+        <v>12.7299995422363</v>
+      </c>
+      <c r="D2600" t="n">
+        <v>12.2299995422363</v>
+      </c>
+      <c r="E2600" t="n">
+        <v>12.710000038147</v>
+      </c>
+      <c r="F2600" t="n">
+        <v>12.3699998855591</v>
+      </c>
+      <c r="G2600" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H2600" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="1769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1770">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5315,10 +5315,13 @@
     <t xml:space="preserve">12.3699998855591</t>
   </si>
   <si>
+    <t xml:space="preserve">13.1099996566772</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">13.1099996566772</t>
+    <t xml:space="preserve">12.960000038147</t>
   </si>
 </sst>
 </file>
@@ -73245,7 +73248,9 @@
       <c r="E2600" t="n">
         <v>12.5600004196167</v>
       </c>
-      <c r="F2600"/>
+      <c r="F2600" t="n">
+        <v>13.1099996566772</v>
+      </c>
       <c r="G2600" t="s">
         <v>1767</v>
       </c>
@@ -73255,27 +73260,51 @@
     </row>
     <row r="2601">
       <c r="A2601" s="1" t="n">
-        <v>46106.693900463</v>
+        <v>46107.3333333333</v>
       </c>
       <c r="B2601" t="n">
-        <v>4606025</v>
+        <v>3908622</v>
       </c>
       <c r="C2601" t="n">
-        <v>13.3299999237061</v>
+        <v>13.3599996566772</v>
       </c>
       <c r="D2601" t="n">
-        <v>12.5600004196167</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="E2601" t="n">
-        <v>12.5600004196167</v>
-      </c>
-      <c r="F2601" t="n">
-        <v>13.1099996566772</v>
-      </c>
+        <v>13.3000001907349</v>
+      </c>
+      <c r="F2601"/>
       <c r="G2601" t="s">
         <v>1768</v>
       </c>
       <c r="H2601" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" s="1" t="n">
+        <v>46107.6921064815</v>
+      </c>
+      <c r="B2602" t="n">
+        <v>3908622</v>
+      </c>
+      <c r="C2602" t="n">
+        <v>13.3599996566772</v>
+      </c>
+      <c r="D2602" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="E2602" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="F2602" t="n">
+        <v>12.960000038147</v>
+      </c>
+      <c r="G2602" t="s">
+        <v>1769</v>
+      </c>
+      <c r="H2602" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="1772">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5325,6 +5325,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.710000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
   </si>
 </sst>
 </file>
@@ -73313,6 +73316,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2603">
+      <c r="A2603" s="1" t="n">
+        <v>46111.2916666667</v>
+      </c>
+      <c r="B2603" t="n">
+        <v>2511670</v>
+      </c>
+      <c r="C2603" t="n">
+        <v>13.0699996948242</v>
+      </c>
+      <c r="D2603" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="E2603" t="n">
+        <v>12.6199998855591</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2603" t="s">
+        <v>1771</v>
+      </c>
+      <c r="H2603" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="1773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="1774">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5331,6 +5331,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.0799999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5</t>
   </si>
 </sst>
 </file>
@@ -73397,6 +73400,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2606">
+      <c r="A2606" s="1" t="n">
+        <v>46114.2916666667</v>
+      </c>
+      <c r="B2606" t="n">
+        <v>2464204</v>
+      </c>
+      <c r="C2606" t="n">
+        <v>13.4899997711182</v>
+      </c>
+      <c r="D2606" t="n">
+        <v>13.1599998474121</v>
+      </c>
+      <c r="E2606" t="n">
+        <v>13.4499998092651</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G2606" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H2606" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -73408,7 +73408,7 @@
         <v>2464204</v>
       </c>
       <c r="C2606" t="n">
-        <v>13.4899997711182</v>
+        <v>13.5</v>
       </c>
       <c r="D2606" t="n">
         <v>13.1599998474121</v>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1777">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5340,6 +5340,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.9849996566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.039999961853</t>
   </si>
 </sst>
 </file>
@@ -73484,6 +73487,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2609">
+      <c r="A2609" s="1" t="n">
+        <v>46121.2916666667</v>
+      </c>
+      <c r="B2609" t="n">
+        <v>1877049</v>
+      </c>
+      <c r="C2609" t="n">
+        <v>14.039999961853</v>
+      </c>
+      <c r="D2609" t="n">
+        <v>13.6499996185303</v>
+      </c>
+      <c r="E2609" t="n">
+        <v>14.0200004577637</v>
+      </c>
+      <c r="F2609" t="n">
+        <v>14.039999961853</v>
+      </c>
+      <c r="G2609" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H2609" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1778">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5343,6 +5343,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.7799997329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.835000038147</t>
   </si>
 </sst>
 </file>
@@ -73539,6 +73542,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2611">
+      <c r="A2611" s="1" t="n">
+        <v>46125.2916666667</v>
+      </c>
+      <c r="B2611" t="n">
+        <v>1737427</v>
+      </c>
+      <c r="C2611" t="n">
+        <v>13.8599996566772</v>
+      </c>
+      <c r="D2611" t="n">
+        <v>13.5799999237061</v>
+      </c>
+      <c r="E2611" t="n">
+        <v>13.6450004577637</v>
+      </c>
+      <c r="F2611" t="n">
+        <v>13.835000038147</v>
+      </c>
+      <c r="G2611" t="s">
+        <v>1777</v>
+      </c>
+      <c r="H2611" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="1778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="1779">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5346,6 +5346,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.835000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6850004196167</t>
   </si>
 </sst>
 </file>
@@ -73568,6 +73571,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2612">
+      <c r="A2612" s="1" t="n">
+        <v>46126.2916666667</v>
+      </c>
+      <c r="B2612" t="n">
+        <v>1504211</v>
+      </c>
+      <c r="C2612" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2612" t="n">
+        <v>13.6199998855591</v>
+      </c>
+      <c r="E2612" t="n">
+        <v>13.9949998855591</v>
+      </c>
+      <c r="F2612" t="n">
+        <v>13.6850004196167</v>
+      </c>
+      <c r="G2612" t="s">
+        <v>1778</v>
+      </c>
+      <c r="H2612" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="1780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1781">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5352,6 +5352,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.664999961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7650003433228</t>
   </si>
 </sst>
 </file>
@@ -73652,6 +73655,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2615">
+      <c r="A2615" s="1" t="n">
+        <v>46129.2916666667</v>
+      </c>
+      <c r="B2615" t="n">
+        <v>2218560</v>
+      </c>
+      <c r="C2615" t="n">
+        <v>13.9250001907349</v>
+      </c>
+      <c r="D2615" t="n">
+        <v>13.6049995422363</v>
+      </c>
+      <c r="E2615" t="n">
+        <v>13.7150001525879</v>
+      </c>
+      <c r="F2615" t="n">
+        <v>13.7650003433228</v>
+      </c>
+      <c r="G2615" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H2615" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1782">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5355,6 +5355,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.7650003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4449996948242</t>
   </si>
 </sst>
 </file>
@@ -73681,6 +73684,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2616">
+      <c r="A2616" s="1" t="n">
+        <v>46132.2916666667</v>
+      </c>
+      <c r="B2616" t="n">
+        <v>1716619</v>
+      </c>
+      <c r="C2616" t="n">
+        <v>13.6400003433228</v>
+      </c>
+      <c r="D2616" t="n">
+        <v>13.3649997711182</v>
+      </c>
+      <c r="E2616" t="n">
+        <v>13.6300001144409</v>
+      </c>
+      <c r="F2616" t="n">
+        <v>13.4449996948242</v>
+      </c>
+      <c r="G2616" t="s">
+        <v>1781</v>
+      </c>
+      <c r="H2616" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="1782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="1783">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5358,6 +5358,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.4449996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0550003051758</t>
   </si>
 </sst>
 </file>
@@ -73710,6 +73713,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2617">
+      <c r="A2617" s="1" t="n">
+        <v>46133.2916666667</v>
+      </c>
+      <c r="B2617" t="n">
+        <v>2571039</v>
+      </c>
+      <c r="C2617" t="n">
+        <v>13.6599998474121</v>
+      </c>
+      <c r="D2617" t="n">
+        <v>13.0349998474121</v>
+      </c>
+      <c r="E2617" t="n">
+        <v>13.5749998092651</v>
+      </c>
+      <c r="F2617" t="n">
+        <v>13.0550003051758</v>
+      </c>
+      <c r="G2617" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H2617" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="1785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="1786">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5367,6 +5367,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1599998474121</t>
   </si>
 </sst>
 </file>
@@ -73797,6 +73800,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2620">
+      <c r="A2620" s="1" t="n">
+        <v>46136.2916666667</v>
+      </c>
+      <c r="B2620" t="n">
+        <v>3282541</v>
+      </c>
+      <c r="C2620" t="n">
+        <v>12.6149997711182</v>
+      </c>
+      <c r="D2620" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="E2620" t="n">
+        <v>12.585000038147</v>
+      </c>
+      <c r="F2620" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="G2620" t="s">
+        <v>1785</v>
+      </c>
+      <c r="H2620" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="1786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="1787">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5370,6 +5370,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.1599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2150001525879</t>
   </si>
 </sst>
 </file>
@@ -73826,6 +73829,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2621">
+      <c r="A2621" s="1" t="n">
+        <v>46139.2916666667</v>
+      </c>
+      <c r="B2621" t="n">
+        <v>1998822</v>
+      </c>
+      <c r="C2621" t="n">
+        <v>12.375</v>
+      </c>
+      <c r="D2621" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="E2621" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F2621" t="n">
+        <v>12.2150001525879</v>
+      </c>
+      <c r="G2621" t="s">
+        <v>1786</v>
+      </c>
+      <c r="H2621" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="1789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="1790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5379,6 +5379,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.7399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -73898,7 +73901,7 @@
         <v>12.0050001144409</v>
       </c>
       <c r="D2623" t="n">
-        <v>11.75</v>
+        <v>11.7399997711182</v>
       </c>
       <c r="E2623" t="n">
         <v>11.960000038147</v>
@@ -73910,6 +73913,32 @@
         <v>1788</v>
       </c>
       <c r="H2623" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" s="1" t="n">
+        <v>46142.2916666667</v>
+      </c>
+      <c r="B2624" t="n">
+        <v>2063888</v>
+      </c>
+      <c r="C2624" t="n">
+        <v>12.0550003051758</v>
+      </c>
+      <c r="D2624" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="E2624" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="F2624" t="n">
+        <v>11.9200000762939</v>
+      </c>
+      <c r="G2624" t="s">
+        <v>1789</v>
+      </c>
+      <c r="H2624" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="1791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="1792">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5385,6 +5385,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6949996948242</t>
   </si>
 </sst>
 </file>
@@ -73945,6 +73948,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2625">
+      <c r="A2625" s="1" t="n">
+        <v>46146.2916666667</v>
+      </c>
+      <c r="B2625" t="n">
+        <v>1627413</v>
+      </c>
+      <c r="C2625" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="D2625" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="E2625" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="F2625" t="n">
+        <v>11.6949996948242</v>
+      </c>
+      <c r="G2625" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H2625" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="1792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="1793">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5388,6 +5388,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.6949996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7200002670288</t>
   </si>
 </sst>
 </file>
@@ -73974,6 +73977,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2626">
+      <c r="A2626" s="1" t="n">
+        <v>46147.2916666667</v>
+      </c>
+      <c r="B2626" t="n">
+        <v>2266056</v>
+      </c>
+      <c r="C2626" t="n">
+        <v>11.8450002670288</v>
+      </c>
+      <c r="D2626" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E2626" t="n">
+        <v>11.789999961853</v>
+      </c>
+      <c r="F2626" t="n">
+        <v>11.7200002670288</v>
+      </c>
+      <c r="G2626" t="s">
+        <v>1792</v>
+      </c>
+      <c r="H2626" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -74029,6 +74029,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2628">
+      <c r="A2628" s="1" t="n">
+        <v>46149.2916666667</v>
+      </c>
+      <c r="B2628" t="n">
+        <v>2252646</v>
+      </c>
+      <c r="C2628" t="n">
+        <v>12.2049999237061</v>
+      </c>
+      <c r="D2628" t="n">
+        <v>11.664999961853</v>
+      </c>
+      <c r="E2628" t="n">
+        <v>12.1549997329712</v>
+      </c>
+      <c r="F2628" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="G2628" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H2628" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="1795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="1796">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5397,6 +5397,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.3649997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2600002288818</t>
   </si>
 </sst>
 </file>
@@ -74087,6 +74090,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2630">
+      <c r="A2630" s="1" t="n">
+        <v>46153.2916666667</v>
+      </c>
+      <c r="B2630" t="n">
+        <v>7516444</v>
+      </c>
+      <c r="C2630" t="n">
+        <v>11.625</v>
+      </c>
+      <c r="D2630" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="E2630" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="F2630" t="n">
+        <v>11.2600002288818</v>
+      </c>
+      <c r="G2630" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H2630" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -74142,6 +74142,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2632">
+      <c r="A2632" s="1" t="n">
+        <v>46155.2916666667</v>
+      </c>
+      <c r="B2632" t="n">
+        <v>3610098</v>
+      </c>
+      <c r="C2632" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="D2632" t="n">
+        <v>11.1149997711182</v>
+      </c>
+      <c r="E2632" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="F2632" t="n">
+        <v>11.5900001525879</v>
+      </c>
+      <c r="G2632" t="s">
+        <v>1580</v>
+      </c>
+      <c r="H2632" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="1798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1799" uniqueCount="1799">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5406,6 +5406,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.0699996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1400003433228</t>
   </si>
 </sst>
 </file>
@@ -74226,6 +74229,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2635">
+      <c r="A2635" s="1" t="n">
+        <v>46160.2916666667</v>
+      </c>
+      <c r="B2635" t="n">
+        <v>1805580</v>
+      </c>
+      <c r="C2635" t="n">
+        <v>11.1850004196167</v>
+      </c>
+      <c r="D2635" t="n">
+        <v>10.7749996185303</v>
+      </c>
+      <c r="E2635" t="n">
+        <v>11.0100002288818</v>
+      </c>
+      <c r="F2635" t="n">
+        <v>11.1400003433228</v>
+      </c>
+      <c r="G2635" t="s">
+        <v>1798</v>
+      </c>
+      <c r="H2635" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="1801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1802">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -5415,6 +5415,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.3850002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5649995803833</t>
   </si>
 </sst>
 </file>
@@ -74287,6 +74290,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2637">
+      <c r="A2637" s="1" t="n">
+        <v>46162.2916666667</v>
+      </c>
+      <c r="B2637" t="n">
+        <v>1597117</v>
+      </c>
+      <c r="C2637" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="D2637" t="n">
+        <v>11.2849998474121</v>
+      </c>
+      <c r="E2637" t="n">
+        <v>11.4949998855591</v>
+      </c>
+      <c r="F2637" t="n">
+        <v>11.5649995803833</v>
+      </c>
+      <c r="G2637" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H2637" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -68989,6 +68989,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2640">
+      <c r="A2640" s="1" t="n">
+        <v>46167.2916666667</v>
+      </c>
+      <c r="B2640" t="n">
+        <v>1468928</v>
+      </c>
+      <c r="C2640" t="n">
+        <v>11.835000038147</v>
+      </c>
+      <c r="D2640" t="n">
+        <v>11.6350002288818</v>
+      </c>
+      <c r="E2640" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F2640" t="n">
+        <v>11.7700004577637</v>
+      </c>
+      <c r="G2640" t="n">
+        <v>11.7700004577637</v>
+      </c>
+      <c r="H2640" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69015,6 +69015,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2641">
+      <c r="A2641" s="1" t="n">
+        <v>46168.2916666667</v>
+      </c>
+      <c r="B2641" t="n">
+        <v>1558343</v>
+      </c>
+      <c r="C2641" t="n">
+        <v>11.9399995803833</v>
+      </c>
+      <c r="D2641" t="n">
+        <v>11.6949996948242</v>
+      </c>
+      <c r="E2641" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="F2641" t="n">
+        <v>11.8100004196167</v>
+      </c>
+      <c r="G2641" t="n">
+        <v>11.8100004196167</v>
+      </c>
+      <c r="H2641" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69041,6 +69041,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2642">
+      <c r="A2642" s="1" t="n">
+        <v>46169.2916666667</v>
+      </c>
+      <c r="B2642" t="n">
+        <v>1669620</v>
+      </c>
+      <c r="C2642" t="n">
+        <v>12.0150003433228</v>
+      </c>
+      <c r="D2642" t="n">
+        <v>11.6949996948242</v>
+      </c>
+      <c r="E2642" t="n">
+        <v>11.8699998855591</v>
+      </c>
+      <c r="F2642" t="n">
+        <v>11.710000038147</v>
+      </c>
+      <c r="G2642" t="n">
+        <v>11.710000038147</v>
+      </c>
+      <c r="H2642" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69064,6 +69064,32 @@
         <v>11.710000038147</v>
       </c>
       <c r="H2642" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" s="1" t="n">
+        <v>46170.2916666667</v>
+      </c>
+      <c r="B2643" t="n">
+        <v>2385990</v>
+      </c>
+      <c r="C2643" t="n">
+        <v>12.1450004577637</v>
+      </c>
+      <c r="D2643" t="n">
+        <v>11.7150001525879</v>
+      </c>
+      <c r="E2643" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="F2643" t="n">
+        <v>12.0500001907349</v>
+      </c>
+      <c r="G2643" t="n">
+        <v>12.0500001907349</v>
+      </c>
+      <c r="H2643" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69093,6 +69093,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2644">
+      <c r="A2644" s="1" t="n">
+        <v>46171.2916666667</v>
+      </c>
+      <c r="B2644" t="n">
+        <v>2957506</v>
+      </c>
+      <c r="C2644" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="D2644" t="n">
+        <v>11.7950000762939</v>
+      </c>
+      <c r="E2644" t="n">
+        <v>12.1000003814697</v>
+      </c>
+      <c r="F2644" t="n">
+        <v>11.835000038147</v>
+      </c>
+      <c r="G2644" t="n">
+        <v>11.835000038147</v>
+      </c>
+      <c r="H2644" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69119,6 +69119,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2645">
+      <c r="A2645" s="1" t="n">
+        <v>46174.2916666667</v>
+      </c>
+      <c r="B2645" t="n">
+        <v>2795482</v>
+      </c>
+      <c r="C2645" t="n">
+        <v>11.875</v>
+      </c>
+      <c r="D2645" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E2645" t="n">
+        <v>11.8599996566772</v>
+      </c>
+      <c r="F2645" t="n">
+        <v>11.3649997711182</v>
+      </c>
+      <c r="G2645" t="n">
+        <v>11.3649997711182</v>
+      </c>
+      <c r="H2645" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69142,6 +69142,32 @@
         <v>11.3649997711182</v>
       </c>
       <c r="H2645" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" s="1" t="n">
+        <v>46175.2916666667</v>
+      </c>
+      <c r="B2646" t="n">
+        <v>2470709</v>
+      </c>
+      <c r="C2646" t="n">
+        <v>11.460000038147</v>
+      </c>
+      <c r="D2646" t="n">
+        <v>11.0550003051758</v>
+      </c>
+      <c r="E2646" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="F2646" t="n">
+        <v>11.0600004196167</v>
+      </c>
+      <c r="G2646" t="n">
+        <v>11.0600004196167</v>
+      </c>
+      <c r="H2646" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69168,6 +69168,32 @@
         <v>11.0600004196167</v>
       </c>
       <c r="H2646" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" s="1" t="n">
+        <v>46176.2916666667</v>
+      </c>
+      <c r="B2647" t="n">
+        <v>2463161</v>
+      </c>
+      <c r="C2647" t="n">
+        <v>11.2299995422363</v>
+      </c>
+      <c r="D2647" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="E2647" t="n">
+        <v>11.0699996948242</v>
+      </c>
+      <c r="F2647" t="n">
+        <v>10.8699998855591</v>
+      </c>
+      <c r="G2647" t="n">
+        <v>10.8699998855591</v>
+      </c>
+      <c r="H2647" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69182,7 +69182,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="D2647" t="n">
-        <v>10.8999996185303</v>
+        <v>10.8699998855591</v>
       </c>
       <c r="E2647" t="n">
         <v>11.0699996948242</v>
@@ -69194,6 +69194,32 @@
         <v>10.8699998855591</v>
       </c>
       <c r="H2647" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" s="1" t="n">
+        <v>46177.2916666667</v>
+      </c>
+      <c r="B2648" t="n">
+        <v>2072826</v>
+      </c>
+      <c r="C2648" t="n">
+        <v>11</v>
+      </c>
+      <c r="D2648" t="n">
+        <v>10.7150001525879</v>
+      </c>
+      <c r="E2648" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="F2648" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="G2648" t="n">
+        <v>10.8000001907349</v>
+      </c>
+      <c r="H2648" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69223,6 +69223,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2649">
+      <c r="A2649" s="1" t="n">
+        <v>46178.2916666667</v>
+      </c>
+      <c r="B2649" t="n">
+        <v>2104111</v>
+      </c>
+      <c r="C2649" t="n">
+        <v>11.085000038147</v>
+      </c>
+      <c r="D2649" t="n">
+        <v>10.7749996185303</v>
+      </c>
+      <c r="E2649" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="F2649" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="G2649" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="H2649" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69246,6 +69246,32 @@
         <v>10.9799995422363</v>
       </c>
       <c r="H2649" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" s="1" t="n">
+        <v>46181.2916666667</v>
+      </c>
+      <c r="B2650" t="n">
+        <v>1941129</v>
+      </c>
+      <c r="C2650" t="n">
+        <v>10.9700002670288</v>
+      </c>
+      <c r="D2650" t="n">
+        <v>10.6850004196167</v>
+      </c>
+      <c r="E2650" t="n">
+        <v>10.9700002670288</v>
+      </c>
+      <c r="F2650" t="n">
+        <v>10.8149995803833</v>
+      </c>
+      <c r="G2650" t="n">
+        <v>10.8149995803833</v>
+      </c>
+      <c r="H2650" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69275,6 +69275,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2651">
+      <c r="A2651" s="1" t="n">
+        <v>46182.2916666667</v>
+      </c>
+      <c r="B2651" t="n">
+        <v>2556753</v>
+      </c>
+      <c r="C2651" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="D2651" t="n">
+        <v>10.7150001525879</v>
+      </c>
+      <c r="E2651" t="n">
+        <v>10.7650003433228</v>
+      </c>
+      <c r="F2651" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="G2651" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="H2651" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69301,6 +69301,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2652">
+      <c r="A2652" s="1" t="n">
+        <v>46183.2916666667</v>
+      </c>
+      <c r="B2652" t="n">
+        <v>1971750</v>
+      </c>
+      <c r="C2652" t="n">
+        <v>11.0500001907349</v>
+      </c>
+      <c r="D2652" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="E2652" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="F2652" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="G2652" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="H2652" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69324,6 +69324,32 @@
         <v>10.960000038147</v>
       </c>
       <c r="H2652" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" s="1" t="n">
+        <v>46184.2916666667</v>
+      </c>
+      <c r="B2653" t="n">
+        <v>5079688</v>
+      </c>
+      <c r="C2653" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="D2653" t="n">
+        <v>10.875</v>
+      </c>
+      <c r="E2653" t="n">
+        <v>10.914999961853</v>
+      </c>
+      <c r="F2653" t="n">
+        <v>11.3649997711182</v>
+      </c>
+      <c r="G2653" t="n">
+        <v>11.3649997711182</v>
+      </c>
+      <c r="H2653" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69353,6 +69353,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2654">
+      <c r="A2654" s="1" t="n">
+        <v>46185.2916666667</v>
+      </c>
+      <c r="B2654" t="n">
+        <v>2661913</v>
+      </c>
+      <c r="C2654" t="n">
+        <v>11.6300001144409</v>
+      </c>
+      <c r="D2654" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E2654" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F2654" t="n">
+        <v>11.4799995422363</v>
+      </c>
+      <c r="G2654" t="n">
+        <v>11.4799995422363</v>
+      </c>
+      <c r="H2654" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69379,6 +69379,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2655">
+      <c r="A2655" s="1" t="n">
+        <v>46188.2916666667</v>
+      </c>
+      <c r="B2655" t="n">
+        <v>1955344</v>
+      </c>
+      <c r="C2655" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="D2655" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="E2655" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="F2655" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="G2655" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="H2655" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69402,6 +69402,32 @@
         <v>11.3500003814697</v>
       </c>
       <c r="H2655" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" s="1" t="n">
+        <v>46189.2916666667</v>
+      </c>
+      <c r="B2656" t="n">
+        <v>2237932</v>
+      </c>
+      <c r="C2656" t="n">
+        <v>11.664999961853</v>
+      </c>
+      <c r="D2656" t="n">
+        <v>11.2700004577637</v>
+      </c>
+      <c r="E2656" t="n">
+        <v>11.4350004196167</v>
+      </c>
+      <c r="F2656" t="n">
+        <v>11.3699998855591</v>
+      </c>
+      <c r="G2656" t="n">
+        <v>11.3699998855591</v>
+      </c>
+      <c r="H2656" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69431,6 +69431,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2657">
+      <c r="A2657" s="1" t="n">
+        <v>46190.2916666667</v>
+      </c>
+      <c r="B2657" t="n">
+        <v>1241372</v>
+      </c>
+      <c r="C2657" t="n">
+        <v>11.4300003051758</v>
+      </c>
+      <c r="D2657" t="n">
+        <v>11.2650003433228</v>
+      </c>
+      <c r="E2657" t="n">
+        <v>11.3500003814697</v>
+      </c>
+      <c r="F2657" t="n">
+        <v>11.3450002670288</v>
+      </c>
+      <c r="G2657" t="n">
+        <v>11.3450002670288</v>
+      </c>
+      <c r="H2657" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69457,6 +69457,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2658">
+      <c r="A2658" s="1" t="n">
+        <v>46191.2916666667</v>
+      </c>
+      <c r="B2658" t="n">
+        <v>1700338</v>
+      </c>
+      <c r="C2658" t="n">
+        <v>11.3950004577637</v>
+      </c>
+      <c r="D2658" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2658" t="n">
+        <v>11.3450002670288</v>
+      </c>
+      <c r="F2658" t="n">
+        <v>11.0649995803833</v>
+      </c>
+      <c r="G2658" t="n">
+        <v>11.0649995803833</v>
+      </c>
+      <c r="H2658" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69483,6 +69483,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2659">
+      <c r="A2659" s="1" t="n">
+        <v>46192.2916666667</v>
+      </c>
+      <c r="B2659" t="n">
+        <v>4412659</v>
+      </c>
+      <c r="C2659" t="n">
+        <v>11.4650001525879</v>
+      </c>
+      <c r="D2659" t="n">
+        <v>10.9650001525879</v>
+      </c>
+      <c r="E2659" t="n">
+        <v>10.9750003814697</v>
+      </c>
+      <c r="F2659" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="G2659" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="H2659" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69506,6 +69506,32 @@
         <v>11.4399995803833</v>
       </c>
       <c r="H2659" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" s="1" t="n">
+        <v>46195.2916666667</v>
+      </c>
+      <c r="B2660" t="n">
+        <v>4138739</v>
+      </c>
+      <c r="C2660" t="n">
+        <v>11.4949998855591</v>
+      </c>
+      <c r="D2660" t="n">
+        <v>10.8699998855591</v>
+      </c>
+      <c r="E2660" t="n">
+        <v>11.4949998855591</v>
+      </c>
+      <c r="F2660" t="n">
+        <v>11.0150003433228</v>
+      </c>
+      <c r="G2660" t="n">
+        <v>11.0150003433228</v>
+      </c>
+      <c r="H2660" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69532,6 +69532,32 @@
         <v>11.0150003433228</v>
       </c>
       <c r="H2660" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" s="1" t="n">
+        <v>46196.2916666667</v>
+      </c>
+      <c r="B2661" t="n">
+        <v>2365198</v>
+      </c>
+      <c r="C2661" t="n">
+        <v>11.0799999237061</v>
+      </c>
+      <c r="D2661" t="n">
+        <v>10.789999961853</v>
+      </c>
+      <c r="E2661" t="n">
+        <v>10.914999961853</v>
+      </c>
+      <c r="F2661" t="n">
+        <v>10.9300003051758</v>
+      </c>
+      <c r="G2661" t="n">
+        <v>10.9300003051758</v>
+      </c>
+      <c r="H2661" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69558,6 +69558,32 @@
         <v>10.9300003051758</v>
       </c>
       <c r="H2661" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" s="1" t="n">
+        <v>46197.2916666667</v>
+      </c>
+      <c r="B2662" t="n">
+        <v>3196945</v>
+      </c>
+      <c r="C2662" t="n">
+        <v>10.9099998474121</v>
+      </c>
+      <c r="D2662" t="n">
+        <v>10.5699996948242</v>
+      </c>
+      <c r="E2662" t="n">
+        <v>10.9099998474121</v>
+      </c>
+      <c r="F2662" t="n">
+        <v>10.6099996566772</v>
+      </c>
+      <c r="G2662" t="n">
+        <v>10.6099996566772</v>
+      </c>
+      <c r="H2662" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69587,6 +69587,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2663">
+      <c r="A2663" s="1" t="n">
+        <v>46198.2916666667</v>
+      </c>
+      <c r="B2663" t="n">
+        <v>3516166</v>
+      </c>
+      <c r="C2663" t="n">
+        <v>10.8249998092651</v>
+      </c>
+      <c r="D2663" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="E2663" t="n">
+        <v>10.7550001144409</v>
+      </c>
+      <c r="F2663" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="G2663" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="H2663" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69610,6 +69610,32 @@
         <v>10.3000001907349</v>
       </c>
       <c r="H2663" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" s="1" t="n">
+        <v>46199.2916666667</v>
+      </c>
+      <c r="B2664" t="n">
+        <v>5678536</v>
+      </c>
+      <c r="C2664" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="D2664" t="n">
+        <v>9.61800003051758</v>
+      </c>
+      <c r="E2664" t="n">
+        <v>10.1450004577637</v>
+      </c>
+      <c r="F2664" t="n">
+        <v>9.93599987030029</v>
+      </c>
+      <c r="G2664" t="n">
+        <v>9.93599987030029</v>
+      </c>
+      <c r="H2664" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69639,6 +69639,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2665">
+      <c r="A2665" s="1" t="n">
+        <v>46202.2916666667</v>
+      </c>
+      <c r="B2665" t="n">
+        <v>2853942</v>
+      </c>
+      <c r="C2665" t="n">
+        <v>10.0050001144409</v>
+      </c>
+      <c r="D2665" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="E2665" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2665" t="n">
+        <v>9.80599975585938</v>
+      </c>
+      <c r="G2665" t="n">
+        <v>9.80599975585938</v>
+      </c>
+      <c r="H2665" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69662,6 +69662,32 @@
         <v>9.80599975585938</v>
       </c>
       <c r="H2665" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" s="1" t="n">
+        <v>46203.2916666667</v>
+      </c>
+      <c r="B2666" t="n">
+        <v>2275216</v>
+      </c>
+      <c r="C2666" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2666" t="n">
+        <v>9.68400001525879</v>
+      </c>
+      <c r="E2666" t="n">
+        <v>9.88799953460693</v>
+      </c>
+      <c r="F2666" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="G2666" t="n">
+        <v>9.94999980926514</v>
+      </c>
+      <c r="H2666" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69688,6 +69688,32 @@
         <v>9.94999980926514</v>
       </c>
       <c r="H2666" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" s="1" t="n">
+        <v>46204.2916666667</v>
+      </c>
+      <c r="B2667" t="n">
+        <v>2653182</v>
+      </c>
+      <c r="C2667" t="n">
+        <v>10.2950000762939</v>
+      </c>
+      <c r="D2667" t="n">
+        <v>9.85000038146973</v>
+      </c>
+      <c r="E2667" t="n">
+        <v>9.97599983215332</v>
+      </c>
+      <c r="F2667" t="n">
+        <v>10.1049995422363</v>
+      </c>
+      <c r="G2667" t="n">
+        <v>10.1049995422363</v>
+      </c>
+      <c r="H2667" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -61692,24 +61692,47 @@
     </row>
     <row r="2667">
       <c r="A2667" s="1" t="n">
-        <v>46205.2916666667</v>
+        <v>46204.2916666667</v>
       </c>
       <c r="B2667" t="n">
-        <v>5470392</v>
+        <v>2653182</v>
       </c>
       <c r="C2667" t="n">
-        <v>10.9949998855591</v>
+        <v>10.2950000762939</v>
       </c>
       <c r="D2667" t="n">
-        <v>10</v>
+        <v>9.85000038146973</v>
       </c>
       <c r="E2667" t="n">
-        <v>10.0799999237061</v>
+        <v>9.97599983215332</v>
       </c>
       <c r="F2667" t="n">
-        <v>10.789999961853</v>
+        <v>10.1049995422363</v>
       </c>
       <c r="G2667" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" s="1" t="n">
+        <v>46206.2916666667</v>
+      </c>
+      <c r="B2668" t="n">
+        <v>2682231</v>
+      </c>
+      <c r="C2668" t="n">
+        <v>11.1149997711182</v>
+      </c>
+      <c r="D2668" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="E2668" t="n">
+        <v>10.8500003814697</v>
+      </c>
+      <c r="F2668" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="G2668" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69792,6 +69792,32 @@
         <v>12.1450004577637</v>
       </c>
       <c r="H2670" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" s="1" t="n">
+        <v>46210.2916666667</v>
+      </c>
+      <c r="B2671" t="n">
+        <v>11577355</v>
+      </c>
+      <c r="C2671" t="n">
+        <v>13.0500001907349</v>
+      </c>
+      <c r="D2671" t="n">
+        <v>12.0649995803833</v>
+      </c>
+      <c r="E2671" t="n">
+        <v>12.335000038147</v>
+      </c>
+      <c r="F2671" t="n">
+        <v>12.5050001144409</v>
+      </c>
+      <c r="G2671" t="n">
+        <v>12.5050001144409</v>
+      </c>
+      <c r="H2671" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69821,6 +69821,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2672">
+      <c r="A2672" s="1" t="n">
+        <v>46211.2916666667</v>
+      </c>
+      <c r="B2672" t="n">
+        <v>5808396</v>
+      </c>
+      <c r="C2672" t="n">
+        <v>12.7600002288818</v>
+      </c>
+      <c r="D2672" t="n">
+        <v>11.8800001144409</v>
+      </c>
+      <c r="E2672" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="F2672" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="G2672" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="H2672" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69847,6 +69847,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2673">
+      <c r="A2673" s="1" t="n">
+        <v>46212.2916666667</v>
+      </c>
+      <c r="B2673" t="n">
+        <v>3971495</v>
+      </c>
+      <c r="C2673" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="D2673" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="E2673" t="n">
+        <v>12.2799997329712</v>
+      </c>
+      <c r="F2673" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="G2673" t="n">
+        <v>11.6800003051758</v>
+      </c>
+      <c r="H2673" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69870,6 +69870,32 @@
         <v>11.6800003051758</v>
       </c>
       <c r="H2673" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" s="1" t="n">
+        <v>46213.2916666667</v>
+      </c>
+      <c r="B2674" t="n">
+        <v>3379802</v>
+      </c>
+      <c r="C2674" t="n">
+        <v>11.9899997711182</v>
+      </c>
+      <c r="D2674" t="n">
+        <v>11.4549999237061</v>
+      </c>
+      <c r="E2674" t="n">
+        <v>11.8249998092651</v>
+      </c>
+      <c r="F2674" t="n">
+        <v>11.5749998092651</v>
+      </c>
+      <c r="G2674" t="n">
+        <v>11.5749998092651</v>
+      </c>
+      <c r="H2674" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69899,6 +69899,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2675">
+      <c r="A2675" s="1" t="n">
+        <v>46216.2916666667</v>
+      </c>
+      <c r="B2675" t="n">
+        <v>2571838</v>
+      </c>
+      <c r="C2675" t="n">
+        <v>11.7950000762939</v>
+      </c>
+      <c r="D2675" t="n">
+        <v>11.4700002670288</v>
+      </c>
+      <c r="E2675" t="n">
+        <v>11.6750001907349</v>
+      </c>
+      <c r="F2675" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="G2675" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="H2675" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69925,6 +69925,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2676">
+      <c r="A2676" s="1" t="n">
+        <v>46217.2916666667</v>
+      </c>
+      <c r="B2676" t="n">
+        <v>3635452</v>
+      </c>
+      <c r="C2676" t="n">
+        <v>12.1149997711182</v>
+      </c>
+      <c r="D2676" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="E2676" t="n">
+        <v>11.8149995803833</v>
+      </c>
+      <c r="F2676" t="n">
+        <v>11.9700002670288</v>
+      </c>
+      <c r="G2676" t="n">
+        <v>11.9700002670288</v>
+      </c>
+      <c r="H2676" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -69951,6 +69951,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2677">
+      <c r="A2677" s="1" t="n">
+        <v>46218.2916666667</v>
+      </c>
+      <c r="B2677" t="n">
+        <v>3011290</v>
+      </c>
+      <c r="C2677" t="n">
+        <v>12.1450004577637</v>
+      </c>
+      <c r="D2677" t="n">
+        <v>11.7950000762939</v>
+      </c>
+      <c r="E2677" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2677" t="n">
+        <v>12.0699996948242</v>
+      </c>
+      <c r="G2677" t="n">
+        <v>12.0699996948242</v>
+      </c>
+      <c r="H2677" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -69974,6 +69974,32 @@
         <v>12.0699996948242</v>
       </c>
       <c r="H2677" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" s="1" t="n">
+        <v>46219.2916666667</v>
+      </c>
+      <c r="B2678" t="n">
+        <v>4560418</v>
+      </c>
+      <c r="C2678" t="n">
+        <v>12.5749998092651</v>
+      </c>
+      <c r="D2678" t="n">
+        <v>11.9899997711182</v>
+      </c>
+      <c r="E2678" t="n">
+        <v>12.0950002670288</v>
+      </c>
+      <c r="F2678" t="n">
+        <v>12.5749998092651</v>
+      </c>
+      <c r="G2678" t="n">
+        <v>12.5749998092651</v>
+      </c>
+      <c r="H2678" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70000,6 +70000,32 @@
         <v>12.5749998092651</v>
       </c>
       <c r="H2678" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" s="1" t="n">
+        <v>46220.2916666667</v>
+      </c>
+      <c r="B2679" t="n">
+        <v>3998498</v>
+      </c>
+      <c r="C2679" t="n">
+        <v>12.585000038147</v>
+      </c>
+      <c r="D2679" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="E2679" t="n">
+        <v>12.4700002670288</v>
+      </c>
+      <c r="F2679" t="n">
+        <v>12.585000038147</v>
+      </c>
+      <c r="G2679" t="n">
+        <v>12.585000038147</v>
+      </c>
+      <c r="H2679" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70029,6 +70029,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2680">
+      <c r="A2680" s="1" t="n">
+        <v>46223.2916666667</v>
+      </c>
+      <c r="B2680" t="n">
+        <v>3650803</v>
+      </c>
+      <c r="C2680" t="n">
+        <v>13.0150003433228</v>
+      </c>
+      <c r="D2680" t="n">
+        <v>12.4300003051758</v>
+      </c>
+      <c r="E2680" t="n">
+        <v>12.5900001525879</v>
+      </c>
+      <c r="F2680" t="n">
+        <v>12.789999961853</v>
+      </c>
+      <c r="G2680" t="n">
+        <v>12.789999961853</v>
+      </c>
+      <c r="H2680" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70052,6 +70052,32 @@
         <v>12.789999961853</v>
       </c>
       <c r="H2680" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" s="1" t="n">
+        <v>46224.2916666667</v>
+      </c>
+      <c r="B2681" t="n">
+        <v>3904726</v>
+      </c>
+      <c r="C2681" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="D2681" t="n">
+        <v>12.6750001907349</v>
+      </c>
+      <c r="E2681" t="n">
+        <v>12.8900003433228</v>
+      </c>
+      <c r="F2681" t="n">
+        <v>12.9250001907349</v>
+      </c>
+      <c r="G2681" t="n">
+        <v>12.9250001907349</v>
+      </c>
+      <c r="H2681" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70078,6 +70078,32 @@
         <v>12.9250001907349</v>
       </c>
       <c r="H2681" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" s="1" t="n">
+        <v>46225.2916666667</v>
+      </c>
+      <c r="B2682" t="n">
+        <v>2458126</v>
+      </c>
+      <c r="C2682" t="n">
+        <v>13.0900001525879</v>
+      </c>
+      <c r="D2682" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="E2682" t="n">
+        <v>12.9949998855591</v>
+      </c>
+      <c r="F2682" t="n">
+        <v>12.9399995803833</v>
+      </c>
+      <c r="G2682" t="n">
+        <v>12.9399995803833</v>
+      </c>
+      <c r="H2682" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70107,6 +70107,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2683">
+      <c r="A2683" s="1" t="n">
+        <v>46226.2916666667</v>
+      </c>
+      <c r="B2683" t="n">
+        <v>2505899</v>
+      </c>
+      <c r="C2683" t="n">
+        <v>13.0950002670288</v>
+      </c>
+      <c r="D2683" t="n">
+        <v>12.7150001525879</v>
+      </c>
+      <c r="E2683" t="n">
+        <v>12.9499998092651</v>
+      </c>
+      <c r="F2683" t="n">
+        <v>12.7150001525879</v>
+      </c>
+      <c r="G2683" t="n">
+        <v>12.7150001525879</v>
+      </c>
+      <c r="H2683" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70130,6 +70130,32 @@
         <v>12.7150001525879</v>
       </c>
       <c r="H2683" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" s="1" t="n">
+        <v>46227.2916666667</v>
+      </c>
+      <c r="B2684" t="n">
+        <v>1647674</v>
+      </c>
+      <c r="C2684" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="D2684" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="E2684" t="n">
+        <v>12.7700004577637</v>
+      </c>
+      <c r="F2684" t="n">
+        <v>12.7749996185303</v>
+      </c>
+      <c r="G2684" t="n">
+        <v>12.7749996185303</v>
+      </c>
+      <c r="H2684" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70156,6 +70156,32 @@
         <v>12.7749996185303</v>
       </c>
       <c r="H2684" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" s="1" t="n">
+        <v>46230.2916666667</v>
+      </c>
+      <c r="B2685" t="n">
+        <v>1971532</v>
+      </c>
+      <c r="C2685" t="n">
+        <v>13.0749998092651</v>
+      </c>
+      <c r="D2685" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="E2685" t="n">
+        <v>12.9750003814697</v>
+      </c>
+      <c r="F2685" t="n">
+        <v>12.8850002288818</v>
+      </c>
+      <c r="G2685" t="n">
+        <v>12.8850002288818</v>
+      </c>
+      <c r="H2685" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70182,6 +70182,32 @@
         <v>12.8850002288818</v>
       </c>
       <c r="H2685" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" s="1" t="n">
+        <v>46231.2916666667</v>
+      </c>
+      <c r="B2686" t="n">
+        <v>2557546</v>
+      </c>
+      <c r="C2686" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="D2686" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="E2686" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2686" t="n">
+        <v>12.8249998092651</v>
+      </c>
+      <c r="G2686" t="n">
+        <v>12.8249998092651</v>
+      </c>
+      <c r="H2686" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70211,6 +70211,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2687">
+      <c r="A2687" s="1" t="n">
+        <v>46232.2916666667</v>
+      </c>
+      <c r="B2687" t="n">
+        <v>5290881</v>
+      </c>
+      <c r="C2687" t="n">
+        <v>13.2399997711182</v>
+      </c>
+      <c r="D2687" t="n">
+        <v>12.2650003433228</v>
+      </c>
+      <c r="E2687" t="n">
+        <v>12.914999961853</v>
+      </c>
+      <c r="F2687" t="n">
+        <v>12.8249998092651</v>
+      </c>
+      <c r="G2687" t="n">
+        <v>12.8249998092651</v>
+      </c>
+      <c r="H2687" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70237,6 +70237,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2688">
+      <c r="A2688" s="1" t="n">
+        <v>46233.2916666667</v>
+      </c>
+      <c r="B2688" t="n">
+        <v>4009611</v>
+      </c>
+      <c r="C2688" t="n">
+        <v>13.2150001525879</v>
+      </c>
+      <c r="D2688" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="E2688" t="n">
+        <v>12.8249998092651</v>
+      </c>
+      <c r="F2688" t="n">
+        <v>13.1800003051758</v>
+      </c>
+      <c r="G2688" t="n">
+        <v>13.1800003051758</v>
+      </c>
+      <c r="H2688" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70242,7 +70242,7 @@
         <v>46233.2916666667</v>
       </c>
       <c r="B2688" t="n">
-        <v>4009611</v>
+        <v>4733180</v>
       </c>
       <c r="C2688" t="n">
         <v>13.2150001525879</v>
@@ -70260,6 +70260,32 @@
         <v>13.1800003051758</v>
       </c>
       <c r="H2688" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" s="1" t="n">
+        <v>46234.2916666667</v>
+      </c>
+      <c r="B2689" t="n">
+        <v>5608936</v>
+      </c>
+      <c r="C2689" t="n">
+        <v>13.9350004196167</v>
+      </c>
+      <c r="D2689" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="E2689" t="n">
+        <v>13.3699998855591</v>
+      </c>
+      <c r="F2689" t="n">
+        <v>13.5550003051758</v>
+      </c>
+      <c r="G2689" t="n">
+        <v>13.5550003051758</v>
+      </c>
+      <c r="H2689" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70289,6 +70289,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2690">
+      <c r="A2690" s="1" t="n">
+        <v>46237.2916666667</v>
+      </c>
+      <c r="B2690" t="n">
+        <v>3309432</v>
+      </c>
+      <c r="C2690" t="n">
+        <v>13.7349996566772</v>
+      </c>
+      <c r="D2690" t="n">
+        <v>13.4099998474121</v>
+      </c>
+      <c r="E2690" t="n">
+        <v>13.6800003051758</v>
+      </c>
+      <c r="F2690" t="n">
+        <v>13.5699996948242</v>
+      </c>
+      <c r="G2690" t="n">
+        <v>13.5699996948242</v>
+      </c>
+      <c r="H2690" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70315,6 +70315,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2691">
+      <c r="A2691" s="1" t="n">
+        <v>46238.2916666667</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>3588721</v>
+      </c>
+      <c r="C2691" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="D2691" t="n">
+        <v>13.4799995422363</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>13.5900001525879</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>13.6300001144409</v>
+      </c>
+      <c r="G2691" t="n">
+        <v>13.6300001144409</v>
+      </c>
+      <c r="H2691" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46234.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>3309432</v>
+        <v>5608936</v>
       </c>
       <c r="C2689" t="n">
-        <v>13.7349996566772</v>
+        <v>13.9350004196167</v>
       </c>
       <c r="D2689" t="n">
-        <v>13.4099998474121</v>
+        <v>13.3000001907349</v>
       </c>
       <c r="E2689" t="n">
-        <v>13.6800003051758</v>
+        <v>13.3699998855591</v>
       </c>
       <c r="F2689" t="n">
-        <v>13.5699996948242</v>
+        <v>13.5550003051758</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>3588721</v>
+        <v>3309432</v>
       </c>
       <c r="C2690" t="n">
-        <v>13.8500003814697</v>
+        <v>13.7349996566772</v>
       </c>
       <c r="D2690" t="n">
-        <v>13.4799995422363</v>
+        <v>13.4099998474121</v>
       </c>
       <c r="E2690" t="n">
-        <v>13.5900001525879</v>
+        <v>13.6800003051758</v>
       </c>
       <c r="F2690" t="n">
-        <v>13.6300001144409</v>
+        <v>13.5699996948242</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,24 +62244,68 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
+        <v>46238.2916666667</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>3588721</v>
+      </c>
+      <c r="C2691" t="n">
+        <v>13.8500003814697</v>
+      </c>
+      <c r="D2691" t="n">
+        <v>13.4799995422363</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>13.5900001525879</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>13.6300001144409</v>
+      </c>
+      <c r="G2691" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="1" t="n">
         <v>46239.2916666667</v>
       </c>
-      <c r="B2691" t="n">
+      <c r="B2692" t="n">
         <v>2911726</v>
       </c>
-      <c r="C2691" t="n">
+      <c r="C2692" t="n">
         <v>13.7700004577637</v>
       </c>
-      <c r="D2691" t="n">
+      <c r="D2692" t="n">
         <v>13.3199996948242</v>
       </c>
-      <c r="E2691" t="n">
+      <c r="E2692" t="n">
         <v>13.6999998092651</v>
       </c>
-      <c r="F2691" t="n">
+      <c r="F2692" t="n">
         <v>13.3199996948242</v>
       </c>
-      <c r="G2691" t="s">
+      <c r="G2692" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="1" t="n">
+        <v>46240.2916666667</v>
+      </c>
+      <c r="B2693" t="n">
+        <v>2213685</v>
+      </c>
+      <c r="C2693" t="n">
+        <v>13.4700002670288</v>
+      </c>
+      <c r="D2693" t="n">
+        <v>13.2200002670288</v>
+      </c>
+      <c r="E2693" t="n">
+        <v>13.289999961853</v>
+      </c>
+      <c r="F2693"/>
+      <c r="G2693" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70419,6 +70419,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2695">
+      <c r="A2695" s="1" t="n">
+        <v>46244.2916666667</v>
+      </c>
+      <c r="B2695" t="n">
+        <v>2144561</v>
+      </c>
+      <c r="C2695" t="n">
+        <v>12.960000038147</v>
+      </c>
+      <c r="D2695" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E2695" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F2695" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G2695" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H2695" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62357,6 +62357,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2696">
+      <c r="A2696" s="1" t="n">
+        <v>46246.2916666667</v>
+      </c>
+      <c r="B2696" t="n">
+        <v>1947518</v>
+      </c>
+      <c r="C2696" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="D2696" t="n">
+        <v>12.5100002288818</v>
+      </c>
+      <c r="E2696" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>12.5100002288818</v>
+      </c>
+      <c r="G2696" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70520,6 +70520,32 @@
         <v>12.8249998092651</v>
       </c>
       <c r="H2698" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" s="1" t="n">
+        <v>46248.2916666667</v>
+      </c>
+      <c r="B2699" t="n">
+        <v>3307114</v>
+      </c>
+      <c r="C2699" t="n">
+        <v>13.3900003433228</v>
+      </c>
+      <c r="D2699" t="n">
+        <v>12.8699998855591</v>
+      </c>
+      <c r="E2699" t="n">
+        <v>12.9250001907349</v>
+      </c>
+      <c r="F2699" t="n">
+        <v>13.2349996566772</v>
+      </c>
+      <c r="G2699" t="n">
+        <v>13.2349996566772</v>
+      </c>
+      <c r="H2699" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70549,6 +70549,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2700">
+      <c r="A2700" s="1" t="n">
+        <v>46251.2916666667</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>3374260</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>13.3800001144409</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>13.2849998474121</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G2700" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H2700" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62449,6 +62449,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2700">
+      <c r="A2700" s="1" t="n">
+        <v>46253.2916666667</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>1443774</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>12.6800003051758</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="G2700" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -61991,22 +61991,22 @@
     </row>
     <row r="2680">
       <c r="A2680" s="1" t="n">
-        <v>46224.2916666667</v>
+        <v>46223.2916666667</v>
       </c>
       <c r="B2680" t="n">
-        <v>3904726</v>
+        <v>3650803</v>
       </c>
       <c r="C2680" t="n">
-        <v>13.1999998092651</v>
+        <v>13.0150003433228</v>
       </c>
       <c r="D2680" t="n">
-        <v>12.6750001907349</v>
+        <v>12.4300003051758</v>
       </c>
       <c r="E2680" t="n">
-        <v>12.8900003433228</v>
+        <v>12.5900001525879</v>
       </c>
       <c r="F2680" t="n">
-        <v>12.9250001907349</v>
+        <v>12.789999961853</v>
       </c>
       <c r="G2680" t="s">
         <v>7</v>
@@ -62014,22 +62014,22 @@
     </row>
     <row r="2681">
       <c r="A2681" s="1" t="n">
-        <v>46225.2916666667</v>
+        <v>46224.2916666667</v>
       </c>
       <c r="B2681" t="n">
-        <v>2458126</v>
+        <v>3904726</v>
       </c>
       <c r="C2681" t="n">
-        <v>13.0900001525879</v>
+        <v>13.1999998092651</v>
       </c>
       <c r="D2681" t="n">
-        <v>12.8199996948242</v>
+        <v>12.6750001907349</v>
       </c>
       <c r="E2681" t="n">
-        <v>12.9949998855591</v>
+        <v>12.8900003433228</v>
       </c>
       <c r="F2681" t="n">
-        <v>12.9399995803833</v>
+        <v>12.9250001907349</v>
       </c>
       <c r="G2681" t="s">
         <v>7</v>
@@ -62037,22 +62037,22 @@
     </row>
     <row r="2682">
       <c r="A2682" s="1" t="n">
-        <v>46226.2916666667</v>
+        <v>46225.2916666667</v>
       </c>
       <c r="B2682" t="n">
-        <v>2505899</v>
+        <v>2458126</v>
       </c>
       <c r="C2682" t="n">
-        <v>13.0950002670288</v>
+        <v>13.0900001525879</v>
       </c>
       <c r="D2682" t="n">
-        <v>12.7150001525879</v>
+        <v>12.8199996948242</v>
       </c>
       <c r="E2682" t="n">
-        <v>12.9499998092651</v>
+        <v>12.9949998855591</v>
       </c>
       <c r="F2682" t="n">
-        <v>12.7150001525879</v>
+        <v>12.9399995803833</v>
       </c>
       <c r="G2682" t="s">
         <v>7</v>
@@ -62060,22 +62060,22 @@
     </row>
     <row r="2683">
       <c r="A2683" s="1" t="n">
-        <v>46227.2916666667</v>
+        <v>46226.2916666667</v>
       </c>
       <c r="B2683" t="n">
-        <v>1647674</v>
+        <v>2505899</v>
       </c>
       <c r="C2683" t="n">
-        <v>12.8199996948242</v>
+        <v>13.0950002670288</v>
       </c>
       <c r="D2683" t="n">
-        <v>12.5200004577637</v>
+        <v>12.7150001525879</v>
       </c>
       <c r="E2683" t="n">
-        <v>12.7700004577637</v>
+        <v>12.9499998092651</v>
       </c>
       <c r="F2683" t="n">
-        <v>12.7749996185303</v>
+        <v>12.7150001525879</v>
       </c>
       <c r="G2683" t="s">
         <v>7</v>
@@ -62083,22 +62083,22 @@
     </row>
     <row r="2684">
       <c r="A2684" s="1" t="n">
-        <v>46230.2916666667</v>
+        <v>46227.2916666667</v>
       </c>
       <c r="B2684" t="n">
-        <v>1971532</v>
+        <v>1647674</v>
       </c>
       <c r="C2684" t="n">
-        <v>13.0749998092651</v>
+        <v>12.8199996948242</v>
       </c>
       <c r="D2684" t="n">
-        <v>12.6800003051758</v>
+        <v>12.5200004577637</v>
       </c>
       <c r="E2684" t="n">
-        <v>12.9750003814697</v>
+        <v>12.7700004577637</v>
       </c>
       <c r="F2684" t="n">
-        <v>12.8850002288818</v>
+        <v>12.7749996185303</v>
       </c>
       <c r="G2684" t="s">
         <v>7</v>
@@ -62106,22 +62106,22 @@
     </row>
     <row r="2685">
       <c r="A2685" s="1" t="n">
-        <v>46231.2916666667</v>
+        <v>46230.2916666667</v>
       </c>
       <c r="B2685" t="n">
-        <v>2557546</v>
+        <v>1971532</v>
       </c>
       <c r="C2685" t="n">
-        <v>13.1000003814697</v>
+        <v>13.0749998092651</v>
       </c>
       <c r="D2685" t="n">
-        <v>12.6999998092651</v>
+        <v>12.6800003051758</v>
       </c>
       <c r="E2685" t="n">
-        <v>13</v>
+        <v>12.9750003814697</v>
       </c>
       <c r="F2685" t="n">
-        <v>12.8249998092651</v>
+        <v>12.8850002288818</v>
       </c>
       <c r="G2685" t="s">
         <v>7</v>
@@ -62129,19 +62129,19 @@
     </row>
     <row r="2686">
       <c r="A2686" s="1" t="n">
-        <v>46232.2916666667</v>
+        <v>46231.2916666667</v>
       </c>
       <c r="B2686" t="n">
-        <v>5290881</v>
+        <v>2557546</v>
       </c>
       <c r="C2686" t="n">
-        <v>13.2399997711182</v>
+        <v>13.1000003814697</v>
       </c>
       <c r="D2686" t="n">
-        <v>12.2650003433228</v>
+        <v>12.6999998092651</v>
       </c>
       <c r="E2686" t="n">
-        <v>12.914999961853</v>
+        <v>13</v>
       </c>
       <c r="F2686" t="n">
         <v>12.8249998092651</v>
@@ -62152,22 +62152,22 @@
     </row>
     <row r="2687">
       <c r="A2687" s="1" t="n">
-        <v>46233.2916666667</v>
+        <v>46232.2916666667</v>
       </c>
       <c r="B2687" t="n">
-        <v>4733180</v>
+        <v>5290881</v>
       </c>
       <c r="C2687" t="n">
-        <v>13.2150001525879</v>
+        <v>13.2399997711182</v>
       </c>
       <c r="D2687" t="n">
-        <v>12.6599998474121</v>
+        <v>12.2650003433228</v>
       </c>
       <c r="E2687" t="n">
+        <v>12.914999961853</v>
+      </c>
+      <c r="F2687" t="n">
         <v>12.8249998092651</v>
-      </c>
-      <c r="F2687" t="n">
-        <v>13.1800003051758</v>
       </c>
       <c r="G2687" t="s">
         <v>7</v>
@@ -62175,22 +62175,22 @@
     </row>
     <row r="2688">
       <c r="A2688" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46233.2916666667</v>
       </c>
       <c r="B2688" t="n">
-        <v>3309432</v>
+        <v>4733180</v>
       </c>
       <c r="C2688" t="n">
-        <v>13.7349996566772</v>
+        <v>13.2150001525879</v>
       </c>
       <c r="D2688" t="n">
-        <v>13.4099998474121</v>
+        <v>12.6599998474121</v>
       </c>
       <c r="E2688" t="n">
-        <v>13.6800003051758</v>
+        <v>12.8249998092651</v>
       </c>
       <c r="F2688" t="n">
-        <v>13.5699996948242</v>
+        <v>13.1800003051758</v>
       </c>
       <c r="G2688" t="s">
         <v>7</v>
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>3588721</v>
+        <v>3309432</v>
       </c>
       <c r="C2689" t="n">
-        <v>13.8500003814697</v>
+        <v>13.7349996566772</v>
       </c>
       <c r="D2689" t="n">
-        <v>13.4799995422363</v>
+        <v>13.4099998474121</v>
       </c>
       <c r="E2689" t="n">
-        <v>13.5900001525879</v>
+        <v>13.6800003051758</v>
       </c>
       <c r="F2689" t="n">
-        <v>13.6300001144409</v>
+        <v>13.5699996948242</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46239.2916666667</v>
+        <v>46238.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>2911726</v>
+        <v>3588721</v>
       </c>
       <c r="C2690" t="n">
-        <v>13.7700004577637</v>
+        <v>13.8500003814697</v>
       </c>
       <c r="D2690" t="n">
-        <v>13.3199996948242</v>
+        <v>13.4799995422363</v>
       </c>
       <c r="E2690" t="n">
-        <v>13.6999998092651</v>
+        <v>13.5900001525879</v>
       </c>
       <c r="F2690" t="n">
-        <v>13.3199996948242</v>
+        <v>13.6300001144409</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,22 +62244,22 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
-        <v>46240.2916666667</v>
+        <v>46239.2916666667</v>
       </c>
       <c r="B2691" t="n">
-        <v>2213685</v>
+        <v>2911726</v>
       </c>
       <c r="C2691" t="n">
-        <v>13.4700002670288</v>
+        <v>13.7700004577637</v>
       </c>
       <c r="D2691" t="n">
-        <v>13.2200002670288</v>
+        <v>13.3199996948242</v>
       </c>
       <c r="E2691" t="n">
-        <v>13.289999961853</v>
+        <v>13.6999998092651</v>
       </c>
       <c r="F2691" t="n">
-        <v>13.2200002670288</v>
+        <v>13.3199996948242</v>
       </c>
       <c r="G2691" t="s">
         <v>7</v>
@@ -62267,22 +62267,22 @@
     </row>
     <row r="2692">
       <c r="A2692" s="1" t="n">
-        <v>46241.2916666667</v>
+        <v>46240.2916666667</v>
       </c>
       <c r="B2692" t="n">
-        <v>3227437</v>
+        <v>2213685</v>
       </c>
       <c r="C2692" t="n">
-        <v>13.3149995803833</v>
+        <v>13.4700002670288</v>
       </c>
       <c r="D2692" t="n">
-        <v>12.8299999237061</v>
+        <v>13.2200002670288</v>
       </c>
       <c r="E2692" t="n">
-        <v>13.2650003433228</v>
+        <v>13.289999961853</v>
       </c>
       <c r="F2692" t="n">
-        <v>12.8800001144409</v>
+        <v>13.2200002670288</v>
       </c>
       <c r="G2692" t="s">
         <v>7</v>
@@ -62290,22 +62290,22 @@
     </row>
     <row r="2693">
       <c r="A2693" s="1" t="n">
-        <v>46244.2916666667</v>
+        <v>46241.2916666667</v>
       </c>
       <c r="B2693" t="n">
-        <v>2144561</v>
+        <v>3227437</v>
       </c>
       <c r="C2693" t="n">
-        <v>12.960000038147</v>
+        <v>13.3149995803833</v>
       </c>
       <c r="D2693" t="n">
-        <v>12.75</v>
+        <v>12.8299999237061</v>
       </c>
       <c r="E2693" t="n">
-        <v>12.8999996185303</v>
+        <v>13.2650003433228</v>
       </c>
       <c r="F2693" t="n">
-        <v>12.75</v>
+        <v>12.8800001144409</v>
       </c>
       <c r="G2693" t="s">
         <v>7</v>
@@ -62313,22 +62313,22 @@
     </row>
     <row r="2694">
       <c r="A2694" s="1" t="n">
-        <v>46245.2916666667</v>
+        <v>46244.2916666667</v>
       </c>
       <c r="B2694" t="n">
-        <v>1989951</v>
+        <v>2144561</v>
       </c>
       <c r="C2694" t="n">
-        <v>12.9200000762939</v>
+        <v>12.960000038147</v>
       </c>
       <c r="D2694" t="n">
-        <v>12.7200002670288</v>
+        <v>12.75</v>
       </c>
       <c r="E2694" t="n">
-        <v>12.7399997711182</v>
+        <v>12.8999996185303</v>
       </c>
       <c r="F2694" t="n">
-        <v>12.7799997329712</v>
+        <v>12.75</v>
       </c>
       <c r="G2694" t="s">
         <v>7</v>
@@ -62336,22 +62336,22 @@
     </row>
     <row r="2695">
       <c r="A2695" s="1" t="n">
-        <v>46246.2916666667</v>
+        <v>46245.2916666667</v>
       </c>
       <c r="B2695" t="n">
-        <v>1947518</v>
+        <v>1989951</v>
       </c>
       <c r="C2695" t="n">
-        <v>12.8199996948242</v>
+        <v>12.9200000762939</v>
       </c>
       <c r="D2695" t="n">
-        <v>12.5100002288818</v>
+        <v>12.7200002670288</v>
       </c>
       <c r="E2695" t="n">
-        <v>12.8199996948242</v>
+        <v>12.7399997711182</v>
       </c>
       <c r="F2695" t="n">
-        <v>12.5100002288818</v>
+        <v>12.7799997329712</v>
       </c>
       <c r="G2695" t="s">
         <v>7</v>
@@ -62359,22 +62359,22 @@
     </row>
     <row r="2696">
       <c r="A2696" s="1" t="n">
-        <v>46247.2916666667</v>
+        <v>46246.2916666667</v>
       </c>
       <c r="B2696" t="n">
-        <v>1798229</v>
+        <v>1947518</v>
       </c>
       <c r="C2696" t="n">
-        <v>12.8599996566772</v>
+        <v>12.8199996948242</v>
       </c>
       <c r="D2696" t="n">
         <v>12.5100002288818</v>
       </c>
       <c r="E2696" t="n">
+        <v>12.8199996948242</v>
+      </c>
+      <c r="F2696" t="n">
         <v>12.5100002288818</v>
-      </c>
-      <c r="F2696" t="n">
-        <v>12.8249998092651</v>
       </c>
       <c r="G2696" t="s">
         <v>7</v>
@@ -62382,22 +62382,22 @@
     </row>
     <row r="2697">
       <c r="A2697" s="1" t="n">
-        <v>46248.2916666667</v>
+        <v>46247.2916666667</v>
       </c>
       <c r="B2697" t="n">
-        <v>3307114</v>
+        <v>1798229</v>
       </c>
       <c r="C2697" t="n">
-        <v>13.3900003433228</v>
+        <v>12.8599996566772</v>
       </c>
       <c r="D2697" t="n">
-        <v>12.8699998855591</v>
+        <v>12.5100002288818</v>
       </c>
       <c r="E2697" t="n">
-        <v>12.9250001907349</v>
+        <v>12.5100002288818</v>
       </c>
       <c r="F2697" t="n">
-        <v>13.2349996566772</v>
+        <v>12.8249998092651</v>
       </c>
       <c r="G2697" t="s">
         <v>7</v>
@@ -62405,22 +62405,22 @@
     </row>
     <row r="2698">
       <c r="A2698" s="1" t="n">
-        <v>46251.2916666667</v>
+        <v>46248.2916666667</v>
       </c>
       <c r="B2698" t="n">
-        <v>3374260</v>
+        <v>3307114</v>
       </c>
       <c r="C2698" t="n">
-        <v>13.3800001144409</v>
+        <v>13.3900003433228</v>
       </c>
       <c r="D2698" t="n">
-        <v>12.75</v>
+        <v>12.8699998855591</v>
       </c>
       <c r="E2698" t="n">
-        <v>13.2849998474121</v>
+        <v>12.9250001907349</v>
       </c>
       <c r="F2698" t="n">
-        <v>12.75</v>
+        <v>13.2349996566772</v>
       </c>
       <c r="G2698" t="s">
         <v>7</v>
@@ -62428,22 +62428,22 @@
     </row>
     <row r="2699">
       <c r="A2699" s="1" t="n">
-        <v>46252.2916666667</v>
+        <v>46251.2916666667</v>
       </c>
       <c r="B2699" t="n">
-        <v>1833820</v>
+        <v>3374260</v>
       </c>
       <c r="C2699" t="n">
-        <v>12.8500003814697</v>
+        <v>13.3800001144409</v>
       </c>
       <c r="D2699" t="n">
-        <v>12.5950002670288</v>
+        <v>12.75</v>
       </c>
       <c r="E2699" t="n">
-        <v>12.7399997711182</v>
+        <v>13.2849998474121</v>
       </c>
       <c r="F2699" t="n">
-        <v>12.6199998855591</v>
+        <v>12.75</v>
       </c>
       <c r="G2699" t="s">
         <v>7</v>
@@ -62451,24 +62451,70 @@
     </row>
     <row r="2700">
       <c r="A2700" s="1" t="n">
+        <v>46252.2916666667</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>1833820</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>12.5950002670288</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>12.7399997711182</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>12.6199998855591</v>
+      </c>
+      <c r="G2700" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="1" t="n">
         <v>46253.2916666667</v>
       </c>
-      <c r="B2700" t="n">
+      <c r="B2701" t="n">
         <v>1443774</v>
       </c>
-      <c r="C2700" t="n">
+      <c r="C2701" t="n">
         <v>12.6800003051758</v>
       </c>
-      <c r="D2700" t="n">
+      <c r="D2701" t="n">
         <v>12.4099998474121</v>
       </c>
-      <c r="E2700" t="n">
+      <c r="E2701" t="n">
         <v>12.6499996185303</v>
       </c>
-      <c r="F2700" t="n">
+      <c r="F2701" t="n">
         <v>12.4099998474121</v>
       </c>
-      <c r="G2700" t="s">
+      <c r="G2701" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="1" t="n">
+        <v>46254.2916666667</v>
+      </c>
+      <c r="B2702" t="n">
+        <v>2014373</v>
+      </c>
+      <c r="C2702" t="n">
+        <v>12.5699996948242</v>
+      </c>
+      <c r="D2702" t="n">
+        <v>12.2200002670288</v>
+      </c>
+      <c r="E2702" t="n">
+        <v>12.4300003051758</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="G2702" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70676,6 +70676,32 @@
         <v>12.4949998855591</v>
       </c>
       <c r="H2704" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" s="1" t="n">
+        <v>46258.2916666667</v>
+      </c>
+      <c r="B2705" t="n">
+        <v>1818854</v>
+      </c>
+      <c r="C2705" t="n">
+        <v>12.6850004196167</v>
+      </c>
+      <c r="D2705" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="E2705" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="F2705" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G2705" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H2705" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70702,6 +70702,32 @@
         <v>12.5</v>
       </c>
       <c r="H2705" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" s="1" t="n">
+        <v>46259.2916666667</v>
+      </c>
+      <c r="B2706" t="n">
+        <v>1515417</v>
+      </c>
+      <c r="C2706" t="n">
+        <v>12.8599996566772</v>
+      </c>
+      <c r="D2706" t="n">
+        <v>12.4750003814697</v>
+      </c>
+      <c r="E2706" t="n">
+        <v>12.5249996185303</v>
+      </c>
+      <c r="F2706" t="n">
+        <v>12.6300001144409</v>
+      </c>
+      <c r="G2706" t="n">
+        <v>12.6300001144409</v>
+      </c>
+      <c r="H2706" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70710,7 +70710,7 @@
         <v>46259.2916666667</v>
       </c>
       <c r="B2706" t="n">
-        <v>1515417</v>
+        <v>1544346</v>
       </c>
       <c r="C2706" t="n">
         <v>12.8599996566772</v>
@@ -70728,6 +70728,32 @@
         <v>12.6300001144409</v>
       </c>
       <c r="H2706" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" s="1" t="n">
+        <v>46260.2916666667</v>
+      </c>
+      <c r="B2707" t="n">
+        <v>2288942</v>
+      </c>
+      <c r="C2707" t="n">
+        <v>13.0450000762939</v>
+      </c>
+      <c r="D2707" t="n">
+        <v>12.6350002288818</v>
+      </c>
+      <c r="E2707" t="n">
+        <v>12.7250003814697</v>
+      </c>
+      <c r="F2707" t="n">
+        <v>12.9099998474121</v>
+      </c>
+      <c r="G2707" t="n">
+        <v>12.9099998474121</v>
+      </c>
+      <c r="H2707" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62649,8 +62649,31 @@
       <c r="E2708" t="n">
         <v>12.9499998092651</v>
       </c>
-      <c r="F2708"/>
+      <c r="F2708" t="n">
+        <v>12.7399997711182</v>
+      </c>
       <c r="G2708" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" s="1" t="n">
+        <v>46262.2916666667</v>
+      </c>
+      <c r="B2709" t="n">
+        <v>1192008</v>
+      </c>
+      <c r="C2709" t="n">
+        <v>12.8549995422363</v>
+      </c>
+      <c r="D2709" t="n">
+        <v>12.4849996566772</v>
+      </c>
+      <c r="E2709" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="F2709"/>
+      <c r="G2709" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62672,8 +62672,31 @@
       <c r="E2709" t="n">
         <v>12.8500003814697</v>
       </c>
-      <c r="F2709"/>
+      <c r="F2709" t="n">
+        <v>12.5200004577637</v>
+      </c>
       <c r="G2709" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" s="1" t="n">
+        <v>46265.2916666667</v>
+      </c>
+      <c r="B2710" t="n">
+        <v>1199097</v>
+      </c>
+      <c r="C2710" t="n">
+        <v>12.6049995422363</v>
+      </c>
+      <c r="D2710" t="n">
+        <v>12.3249998092651</v>
+      </c>
+      <c r="E2710" t="n">
+        <v>12.4899997711182</v>
+      </c>
+      <c r="F2710"/>
+      <c r="G2710" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70861,6 +70861,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2712">
+      <c r="A2712" s="1" t="n">
+        <v>46267.2916666667</v>
+      </c>
+      <c r="B2712" t="n">
+        <v>1381239</v>
+      </c>
+      <c r="C2712" t="n">
+        <v>12.1949996948242</v>
+      </c>
+      <c r="D2712" t="n">
+        <v>11.9750003814697</v>
+      </c>
+      <c r="E2712" t="n">
+        <v>12.1599998474121</v>
+      </c>
+      <c r="F2712" t="n">
+        <v>12.1300001144409</v>
+      </c>
+      <c r="G2712" t="n">
+        <v>12.1300001144409</v>
+      </c>
+      <c r="H2712" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70887,6 +70887,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2713">
+      <c r="A2713" s="1" t="n">
+        <v>46268.2916666667</v>
+      </c>
+      <c r="B2713" t="n">
+        <v>1172625</v>
+      </c>
+      <c r="C2713" t="n">
+        <v>12.4300003051758</v>
+      </c>
+      <c r="D2713" t="n">
+        <v>12.0699996948242</v>
+      </c>
+      <c r="E2713" t="n">
+        <v>12.1899995803833</v>
+      </c>
+      <c r="F2713" t="n">
+        <v>12.1949996948242</v>
+      </c>
+      <c r="G2713" t="n">
+        <v>12.1949996948242</v>
+      </c>
+      <c r="H2713" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -70910,6 +70910,32 @@
         <v>12.1949996948242</v>
       </c>
       <c r="H2713" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" s="1" t="n">
+        <v>46269.2916666667</v>
+      </c>
+      <c r="B2714" t="n">
+        <v>804073</v>
+      </c>
+      <c r="C2714" t="n">
+        <v>12.3199996948242</v>
+      </c>
+      <c r="D2714" t="n">
+        <v>12.0900001525879</v>
+      </c>
+      <c r="E2714" t="n">
+        <v>12.2200002670288</v>
+      </c>
+      <c r="F2714" t="n">
+        <v>12.2150001525879</v>
+      </c>
+      <c r="G2714" t="n">
+        <v>12.2150001525879</v>
+      </c>
+      <c r="H2714" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -70939,6 +70939,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2715">
+      <c r="A2715" s="1" t="n">
+        <v>46272.2916666667</v>
+      </c>
+      <c r="B2715" t="n">
+        <v>824125</v>
+      </c>
+      <c r="C2715" t="n">
+        <v>12.4300003051758</v>
+      </c>
+      <c r="D2715" t="n">
+        <v>12.1899995803833</v>
+      </c>
+      <c r="E2715" t="n">
+        <v>12.2399997711182</v>
+      </c>
+      <c r="F2715" t="n">
+        <v>12.3299999237061</v>
+      </c>
+      <c r="G2715" t="n">
+        <v>12.3299999237061</v>
+      </c>
+      <c r="H2715" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62817,6 +62817,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2716">
+      <c r="A2716" s="1" t="n">
+        <v>46274.2916666667</v>
+      </c>
+      <c r="B2716" t="n">
+        <v>1487560</v>
+      </c>
+      <c r="C2716" t="n">
+        <v>12.6949996948242</v>
+      </c>
+      <c r="D2716" t="n">
+        <v>12.0950002670288</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>12.6949996948242</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>12.1350002288818</v>
+      </c>
+      <c r="G2716" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" s="1" t="n">
+        <v>46275.2916666667</v>
+      </c>
+      <c r="B2717" t="n">
+        <v>1152687</v>
+      </c>
+      <c r="C2717" t="n">
+        <v>12.3900003433228</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>12.2049999237061</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>12.3050003051758</v>
+      </c>
+      <c r="G2717" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>1104653</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>12.210000038147</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>12.210000038147</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>12.4499998092651</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
